--- a/results/GSE186332/glass_recurrence_score_gse186332_universe.xlsx
+++ b/results/GSE186332/glass_recurrence_score_gse186332_universe.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.2292</t>
+          <t>0.2325</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.2316</t>
+          <t>0.2357</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.02e-15</t>
+          <t>5.87e-15</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.59e-12</t>
+          <t>1.62e-12</t>
         </is>
       </c>
     </row>
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3726840218516593</v>
+        <v>0.3517171867968006</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6297590932610285</v>
+        <v>0.6145295737119844</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2570750714093692</v>
+        <v>-0.2628123869151837</v>
       </c>
     </row>
     <row r="3">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3905329573286433</v>
+        <v>0.3666726469300514</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4713196971755463</v>
+        <v>0.4497405787934622</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.08078673984690299</v>
+        <v>-0.08306793186341083</v>
       </c>
     </row>
     <row r="4">
@@ -571,13 +571,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.335239992054843</v>
+        <v>0.321586044422444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5930832535995815</v>
+        <v>0.5835212532885993</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2578432615447385</v>
+        <v>-0.2619352088661552</v>
       </c>
     </row>
     <row r="5">
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3855903594357616</v>
+        <v>0.3679935430616068</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6191829289796297</v>
+        <v>0.6051091310764606</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.233592569543868</v>
+        <v>-0.2371155880148538</v>
       </c>
     </row>
     <row r="6">
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3059884762188321</v>
+        <v>0.2897219352132314</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4635875707847825</v>
+        <v>0.4486436151521541</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1575990945659504</v>
+        <v>-0.1589216799389228</v>
       </c>
     </row>
     <row r="7">
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4509339069483371</v>
+        <v>0.4381573106100786</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4579663412758749</v>
+        <v>0.4439456162705068</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.007032434327537862</v>
+        <v>-0.005788305660428261</v>
       </c>
     </row>
     <row r="8">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3433146088063228</v>
+        <v>0.3242957148575497</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5154310103109472</v>
+        <v>0.497803017108355</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1721164015046244</v>
+        <v>-0.1735073022508053</v>
       </c>
     </row>
     <row r="9">
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7637893278042088</v>
+        <v>0.7541570469546709</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3124954833599755</v>
+        <v>0.293325098467001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4512938444442334</v>
+        <v>0.4608319484876699</v>
       </c>
     </row>
     <row r="10">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4423119250446295</v>
+        <v>0.424864974819599</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6442080053650456</v>
+        <v>0.6310428488054097</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2018960803204161</v>
+        <v>-0.2061778739858107</v>
       </c>
     </row>
     <row r="11">
@@ -683,13 +683,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6388905521595012</v>
+        <v>0.6225100605927271</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3919858184729854</v>
+        <v>0.3674919866653222</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2469047336865158</v>
+        <v>0.2550180739274049</v>
       </c>
     </row>
     <row r="12">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3365967390994635</v>
+        <v>0.3139175570493119</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5568135502091385</v>
+        <v>0.5388322073414064</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2202168111096749</v>
+        <v>-0.2249146502920945</v>
       </c>
     </row>
     <row r="13">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2700221878005502</v>
+        <v>0.2518140496030109</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5437283020613224</v>
+        <v>0.5261689996241601</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2737061142607722</v>
+        <v>-0.2743549500211492</v>
       </c>
     </row>
     <row r="14">
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2940769350524715</v>
+        <v>0.2761733647799154</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6185657752866802</v>
+        <v>0.604905933076051</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3244888402342088</v>
+        <v>-0.3287325682961356</v>
       </c>
     </row>
     <row r="15">
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4299060827939863</v>
+        <v>0.4126455943137735</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5781248645007993</v>
+        <v>0.5640593154824654</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1482187817068129</v>
+        <v>-0.1514137211686918</v>
       </c>
     </row>
     <row r="16">
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4338134151745065</v>
+        <v>0.4155030252711962</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5549758197159648</v>
+        <v>0.5398168773509092</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1211624045414583</v>
+        <v>-0.124313852079713</v>
       </c>
     </row>
     <row r="17">
@@ -779,13 +779,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3689404241243706</v>
+        <v>0.3484435382381096</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6432338564445588</v>
+        <v>0.628466206491947</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2742934323201882</v>
+        <v>-0.2800226682538373</v>
       </c>
     </row>
     <row r="18">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5911498219566312</v>
+        <v>0.5733911454561567</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4910028530711708</v>
+        <v>0.4694484931264074</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1001469688854605</v>
+        <v>0.1039426523297493</v>
       </c>
     </row>
     <row r="19">
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4027298469070669</v>
+        <v>0.3854742457993015</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5971821947546272</v>
+        <v>0.5828620056406543</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1944523478475603</v>
+        <v>-0.1973877598413528</v>
       </c>
     </row>
     <row r="20">
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5854548292637805</v>
+        <v>0.5691320629857054</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4686295863769465</v>
+        <v>0.448071834312656</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1168252428868339</v>
+        <v>0.1210602286730494</v>
       </c>
     </row>
     <row r="21">
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4464236676479734</v>
+        <v>0.4228836306222661</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4803074494931246</v>
+        <v>0.4587378195785092</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.03388378184515128</v>
+        <v>-0.03585418895624315</v>
       </c>
     </row>
     <row r="22">
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6052611474805304</v>
+        <v>0.589701549935854</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3861915113183386</v>
+        <v>0.3666261034568105</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2190696361621918</v>
+        <v>0.2230754464790435</v>
       </c>
     </row>
     <row r="23">
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3446154011333823</v>
+        <v>0.3299320039687996</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5894142965748693</v>
+        <v>0.5763291135372647</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.244798895441487</v>
+        <v>-0.2463971095684651</v>
       </c>
     </row>
     <row r="24">
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6104374750423377</v>
+        <v>0.5968521115786193</v>
       </c>
       <c r="C24" t="n">
-        <v>0.491287582058316</v>
+        <v>0.4737920413607237</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1191498929840217</v>
+        <v>0.1230600702178956</v>
       </c>
     </row>
     <row r="25">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4006983396521557</v>
+        <v>0.3818247573300787</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6692757188322931</v>
+        <v>0.6558146712011905</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2685773791801374</v>
+        <v>-0.2739899138711118</v>
       </c>
     </row>
     <row r="26">
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.535691057279874</v>
+        <v>0.5203387884684808</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5777411307643167</v>
+        <v>0.5626781802014869</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04205007348444267</v>
+        <v>-0.04233939173300605</v>
       </c>
     </row>
     <row r="27">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2509158197407418</v>
+        <v>0.2333891636754437</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5897806864136578</v>
+        <v>0.5752161079485557</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.338864866672916</v>
+        <v>-0.341826944273112</v>
       </c>
     </row>
     <row r="28">
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3098503841053915</v>
+        <v>0.2903003183508092</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6133514047111808</v>
+        <v>0.5984528687585366</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3035010206057893</v>
+        <v>-0.3081525504077274</v>
       </c>
     </row>
     <row r="29">
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5546483504095018</v>
+        <v>0.5380892578318534</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5352724292730305</v>
+        <v>0.5181923322547033</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01937592113647124</v>
+        <v>0.01989692557715006</v>
       </c>
     </row>
     <row r="30">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2230468603209199</v>
+        <v>0.21300475932932</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5510864506580565</v>
+        <v>0.5413714184442672</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3280395903371366</v>
+        <v>-0.3283666591149472</v>
       </c>
     </row>
     <row r="31">
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6976723250444643</v>
+        <v>0.6848981761942738</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4034797640073654</v>
+        <v>0.3837699798635366</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2941925610370989</v>
+        <v>0.3011281963307373</v>
       </c>
     </row>
     <row r="32">
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7020867599575653</v>
+        <v>0.6906195858427522</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3888436823407325</v>
+        <v>0.3694720213159286</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3132430776168328</v>
+        <v>0.3211475645268236</v>
       </c>
     </row>
     <row r="33">
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2977018096705444</v>
+        <v>0.2795925912830459</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5776573019254617</v>
+        <v>0.5617943452899314</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2799554922549173</v>
+        <v>-0.2822017540068856</v>
       </c>
     </row>
     <row r="34">
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4775183855639306</v>
+        <v>0.4630125074807857</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4385101013750821</v>
+        <v>0.423421090424638</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03900828418884855</v>
+        <v>0.03959141705614766</v>
       </c>
     </row>
     <row r="35">
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.704730259031112</v>
+        <v>0.692607696031506</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3988352127373584</v>
+        <v>0.3756771993509886</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3058950462937535</v>
+        <v>0.3169304966805173</v>
       </c>
     </row>
     <row r="36">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.2305753507700071</v>
+        <v>0.2133341103310578</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5552504314294552</v>
+        <v>0.540638072277376</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3246750806594481</v>
+        <v>-0.3273039619463183</v>
       </c>
     </row>
     <row r="37">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.2490061327196346</v>
+        <v>0.2299166822720985</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5032751060145746</v>
+        <v>0.4833354722596535</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2542689732949399</v>
+        <v>-0.253418789987555</v>
       </c>
     </row>
     <row r="38">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5950451787887435</v>
+        <v>0.5802619006150067</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5049856479246582</v>
+        <v>0.4882343774349385</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09005953086408536</v>
+        <v>0.09202752318006818</v>
       </c>
     </row>
     <row r="39">
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3507252020460844</v>
+        <v>0.3339254667115404</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5138425983471265</v>
+        <v>0.5002276428726392</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1631173963010421</v>
+        <v>-0.1663021761610988</v>
       </c>
     </row>
     <row r="40">
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.673454049614284</v>
+        <v>0.6602284984431672</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4838568058899876</v>
+        <v>0.4660495100330923</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1895972437242964</v>
+        <v>0.194178988410075</v>
       </c>
     </row>
     <row r="41">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3255065553739034</v>
+        <v>0.3049331934737429</v>
       </c>
       <c r="C41" t="n">
-        <v>0.583483406225881</v>
+        <v>0.5667864465405922</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2579768508519776</v>
+        <v>-0.2618532530668493</v>
       </c>
     </row>
     <row r="42">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.225901789766357</v>
+        <v>0.2076037521132811</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6347252293007807</v>
+        <v>0.6198241802564878</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4088234395344237</v>
+        <v>-0.4122204281432067</v>
       </c>
     </row>
     <row r="43">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3509558345904217</v>
+        <v>0.3322547033461974</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4812787077639958</v>
+        <v>0.4653448102008452</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.130322873173574</v>
+        <v>-0.1330901068546478</v>
       </c>
     </row>
     <row r="44">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5365801385116705</v>
+        <v>0.5195967119900788</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3365922998875537</v>
+        <v>0.3175201746586121</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1999878386241168</v>
+        <v>0.2020765373314667</v>
       </c>
     </row>
     <row r="45">
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2922430243462899</v>
+        <v>0.2778196832730287</v>
       </c>
       <c r="C45" t="n">
-        <v>0.503781692359724</v>
+        <v>0.4899264209345887</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2115386680134341</v>
+        <v>-0.21210673766156</v>
       </c>
     </row>
     <row r="46">
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2782196571606966</v>
+        <v>0.2610238734733413</v>
       </c>
       <c r="C46" t="n">
-        <v>0.588312959071292</v>
+        <v>0.5738410838856346</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3100933019105954</v>
+        <v>-0.3128172104122933</v>
       </c>
     </row>
     <row r="47">
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5071921427188045</v>
+        <v>0.4909150195842713</v>
       </c>
       <c r="C47" t="n">
-        <v>0.629041489493934</v>
+        <v>0.6150467355400941</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1218493467751295</v>
+        <v>-0.1241317159558229</v>
       </c>
     </row>
     <row r="48">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2730284634008658</v>
+        <v>0.2549028338154648</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6080741625065401</v>
+        <v>0.5939790751893714</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3350456991056743</v>
+        <v>-0.3390762413739066</v>
       </c>
     </row>
     <row r="49">
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6442564237461084</v>
+        <v>0.630228965514833</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3610013065736264</v>
+        <v>0.3412863197328175</v>
       </c>
       <c r="D49" t="n">
-        <v>0.283255117172482</v>
+        <v>0.2889426457820155</v>
       </c>
     </row>
     <row r="50">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6079608077466105</v>
+        <v>0.5916228732415516</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3925328739127543</v>
+        <v>0.3721601933589393</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2154279338338562</v>
+        <v>0.2194626798826123</v>
       </c>
     </row>
     <row r="51">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4684111874747325</v>
+        <v>0.4523353365033094</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4813365207563096</v>
+        <v>0.465768012051322</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.01292533328157708</v>
+        <v>-0.01343267554801264</v>
       </c>
     </row>
     <row r="52">
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3611457874356676</v>
+        <v>0.3449088533652513</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6155334838398233</v>
+        <v>0.602559225341999</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2543876964041558</v>
+        <v>-0.2576503719767477</v>
       </c>
     </row>
     <row r="53">
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5371681792334907</v>
+        <v>0.5184910180372602</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5344984578384301</v>
+        <v>0.5152268636923367</v>
       </c>
       <c r="D53" t="n">
-        <v>0.002669721395060609</v>
+        <v>0.003264154344923442</v>
       </c>
     </row>
     <row r="54">
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2328583445414831</v>
+        <v>0.2154112696972197</v>
       </c>
       <c r="C54" t="n">
-        <v>0.6347367918992435</v>
+        <v>0.6200350172794691</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4018784473577603</v>
+        <v>-0.4046237475822494</v>
       </c>
     </row>
     <row r="55">
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5858508482611298</v>
+        <v>0.576815173630618</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3575993733071632</v>
+        <v>0.3471565266281049</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2282514749539665</v>
+        <v>0.2296586470025131</v>
       </c>
     </row>
     <row r="56">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2700589403456639</v>
+        <v>0.2557191179417068</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5208408610667076</v>
+        <v>0.5067215759609126</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.2507819207210437</v>
+        <v>-0.2510024580192058</v>
       </c>
     </row>
     <row r="57">
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2302507721131599</v>
+        <v>0.214814116389894</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6276135085837841</v>
+        <v>0.6136029602740269</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.3973627364706242</v>
+        <v>-0.3987888438841329</v>
       </c>
     </row>
     <row r="58">
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2709682561247704</v>
+        <v>0.2522558033654477</v>
       </c>
       <c r="C58" t="n">
-        <v>0.448965581035026</v>
+        <v>0.4320677000736403</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.1779973249102557</v>
+        <v>-0.1798118967081925</v>
       </c>
     </row>
     <row r="59">
@@ -1451,13 +1451,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2558220780384547</v>
+        <v>0.2383161149764566</v>
       </c>
       <c r="C59" t="n">
-        <v>0.6601123595505618</v>
+        <v>0.6466256909495917</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4042902815121071</v>
+        <v>-0.4083095759731351</v>
       </c>
     </row>
     <row r="60">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3767218464148306</v>
+        <v>0.3543419549524657</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4998952139514313</v>
+        <v>0.4804677831862058</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.1231733675366007</v>
+        <v>-0.1261258282337401</v>
       </c>
     </row>
     <row r="61">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.234407732735492</v>
+        <v>0.2190666511267122</v>
       </c>
       <c r="C61" t="n">
-        <v>0.51115863017896</v>
+        <v>0.4959123590218384</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.276750897443468</v>
+        <v>-0.2768457078951262</v>
       </c>
     </row>
     <row r="62">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5715797111084774</v>
+        <v>0.5559959997712658</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4057843344134727</v>
+        <v>0.3876124082171438</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1657953766950047</v>
+        <v>0.168383591554122</v>
       </c>
     </row>
     <row r="63">
@@ -1515,13 +1515,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.2279714948911898</v>
+        <v>0.2111454212353478</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6118536868790524</v>
+        <v>0.596718428683613</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.3838821919878627</v>
+        <v>-0.3855730074482653</v>
       </c>
     </row>
     <row r="64">
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5741379360183614</v>
+        <v>0.5571169717692283</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5322419444821835</v>
+        <v>0.5156836772421295</v>
       </c>
       <c r="D64" t="n">
-        <v>0.04189599153617785</v>
+        <v>0.04143329452709876</v>
       </c>
     </row>
     <row r="65">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4437159548579638</v>
+        <v>0.4236920574681485</v>
       </c>
       <c r="C65" t="n">
-        <v>0.444172883972215</v>
+        <v>0.424709793532498</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.0004569291142512144</v>
+        <v>-0.001017736064349517</v>
       </c>
     </row>
     <row r="66">
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.2733732766050229</v>
+        <v>0.2531877641192054</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6484323284471719</v>
+        <v>0.6337084857318337</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.375059051842149</v>
+        <v>-0.3805207216126283</v>
       </c>
     </row>
     <row r="67">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.2575298325364088</v>
+        <v>0.2324478178368121</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5632727067753935</v>
+        <v>0.5449778010004064</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.3057428742389848</v>
+        <v>-0.3125299831635943</v>
       </c>
     </row>
     <row r="68">
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.2312812887011527</v>
+        <v>0.215393372558623</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4910715059995432</v>
+        <v>0.4741785759028561</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.2597902172983906</v>
+        <v>-0.2587852033442331</v>
       </c>
     </row>
     <row r="69">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4167499104930994</v>
+        <v>0.3953477916022261</v>
       </c>
       <c r="C69" t="n">
-        <v>0.473111177274869</v>
+        <v>0.4541284333586949</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.05636126678176961</v>
+        <v>-0.05878064175646885</v>
       </c>
     </row>
     <row r="70">
@@ -1627,13 +1627,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.2923823949527606</v>
+        <v>0.273315715564705</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6169556834507418</v>
+        <v>0.6011307281210755</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.3245732884979812</v>
+        <v>-0.3278150125563705</v>
       </c>
     </row>
     <row r="71">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.384730597650067</v>
+        <v>0.367556372712713</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5934322995406758</v>
+        <v>0.5785887364139983</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.2087017018906088</v>
+        <v>-0.2110323637012854</v>
       </c>
     </row>
     <row r="72">
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.2745328400508589</v>
+        <v>0.2633352234457753</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4985239620399893</v>
+        <v>0.4891495323390382</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.2239911219891303</v>
+        <v>-0.2258143088932629</v>
       </c>
     </row>
     <row r="73">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3555024134859541</v>
+        <v>0.3314074266140927</v>
       </c>
       <c r="C73" t="n">
-        <v>0.4779067649872957</v>
+        <v>0.4560916621596434</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.1224043515013415</v>
+        <v>-0.1246842355455506</v>
       </c>
     </row>
     <row r="74">
@@ -1691,13 +1691,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4821326882504591</v>
+        <v>0.4612053329980894</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5131849755595574</v>
+        <v>0.49545707327656</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.03105228730909831</v>
+        <v>-0.03425174027847067</v>
       </c>
     </row>
     <row r="75">
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4341324190070949</v>
+        <v>0.4190361823395402</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6166781810876358</v>
+        <v>0.6042906098078938</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.182545762080541</v>
+        <v>-0.1852544274683537</v>
       </c>
     </row>
     <row r="76">
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.3756560226065318</v>
+        <v>0.359454425373079</v>
       </c>
       <c r="C76" t="n">
-        <v>0.633963181795845</v>
+        <v>0.6227556551684099</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.2583071591893132</v>
+        <v>-0.2633012297953309</v>
       </c>
     </row>
     <row r="77">
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4396814338943533</v>
+        <v>0.4211855850334524</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5933051109575854</v>
+        <v>0.5783740798797311</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.1536236770632321</v>
+        <v>-0.1571884948462787</v>
       </c>
     </row>
     <row r="78">
@@ -1755,13 +1755,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.3555672466273345</v>
+        <v>0.3366146209145962</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4037550983832596</v>
+        <v>0.3860021022590118</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.0481878517559251</v>
+        <v>-0.04938748134441556</v>
       </c>
     </row>
     <row r="79">
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4510156710374665</v>
+        <v>0.4336254059049208</v>
       </c>
       <c r="C79" t="n">
-        <v>0.5763586775856139</v>
+        <v>0.5603001524748905</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.1253430065481473</v>
+        <v>-0.1266747465699697</v>
       </c>
     </row>
     <row r="80">
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.2203955151984163</v>
+        <v>0.2068402863716782</v>
       </c>
       <c r="C80" t="n">
-        <v>0.5487464697941569</v>
+        <v>0.5344313664378016</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.3283509545957406</v>
+        <v>-0.3275910800661235</v>
       </c>
     </row>
     <row r="81">
@@ -1803,13 +1803,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.2575985887022677</v>
+        <v>0.249440277903276</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3854565636535499</v>
+        <v>0.3774387579560419</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.1278579749512823</v>
+        <v>-0.1279984800527659</v>
       </c>
     </row>
     <row r="82">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.3042334389521643</v>
+        <v>0.2889165639763775</v>
       </c>
       <c r="C82" t="n">
-        <v>0.5486994967379019</v>
+        <v>0.5351815184543508</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.2444660577857375</v>
+        <v>-0.2462649544779733</v>
       </c>
     </row>
     <row r="83">
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5641879070912177</v>
+        <v>0.5515640571329046</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3711066562988701</v>
+        <v>0.354916245756523</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1930812507923476</v>
+        <v>0.1966478113763815</v>
       </c>
     </row>
     <row r="84">
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5844691177448309</v>
+        <v>0.5674139376804174</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3935352066669942</v>
+        <v>0.3701083518961581</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1909339110778367</v>
+        <v>0.1973055857842592</v>
       </c>
     </row>
     <row r="85">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.2490734435606857</v>
+        <v>0.232781752252093</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4404341900255244</v>
+        <v>0.4252613309621807</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.1913607464648387</v>
+        <v>-0.1924795787100878</v>
       </c>
     </row>
     <row r="86">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.2317877718088158</v>
+        <v>0.2070668379553785</v>
       </c>
       <c r="C86" t="n">
-        <v>0.6105695157872829</v>
+        <v>0.5935192060305499</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.3787817439784671</v>
+        <v>-0.3864523680751714</v>
       </c>
     </row>
     <row r="87">
@@ -1899,13 +1899,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5303908447345371</v>
+        <v>0.5148731769472633</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5207317390437154</v>
+        <v>0.5051700904765833</v>
       </c>
       <c r="D87" t="n">
-        <v>0.009659105690821734</v>
+        <v>0.009703086470679967</v>
       </c>
     </row>
     <row r="88">
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7469521196927157</v>
+        <v>0.7412209078738243</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2979255253033015</v>
+        <v>0.2849576950929975</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4490265943894142</v>
+        <v>0.4562632127808268</v>
       </c>
     </row>
     <row r="89">
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.2444950675193808</v>
+        <v>0.224397161077303</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5457904192309138</v>
+        <v>0.527891981165226</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.301295351711533</v>
+        <v>-0.3034948200879229</v>
       </c>
     </row>
     <row r="90">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.2325067176632319</v>
+        <v>0.2240195751044691</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5001824722569904</v>
+        <v>0.4920527428674447</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.2676757545937585</v>
+        <v>-0.2680331677629756</v>
       </c>
     </row>
     <row r="91">
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.730054207939293</v>
+        <v>0.7205379268740377</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4196197061365602</v>
+        <v>0.4011392074361301</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3104345018027328</v>
+        <v>0.3193987194379076</v>
       </c>
     </row>
     <row r="92">
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2507192555668749</v>
+        <v>0.2299406906287527</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6496149654711905</v>
+        <v>0.6353023677914363</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.3988957099043156</v>
+        <v>-0.4053616771626837</v>
       </c>
     </row>
     <row r="93">
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.2843451501713123</v>
+        <v>0.2672119182720619</v>
       </c>
       <c r="C93" t="n">
-        <v>0.5836785250749401</v>
+        <v>0.5698878897047364</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.2993333749036278</v>
+        <v>-0.3026759714326745</v>
       </c>
     </row>
     <row r="94">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.2163991921047274</v>
+        <v>0.2000339172602187</v>
       </c>
       <c r="C94" t="n">
-        <v>0.6095079247159214</v>
+        <v>0.5942380380545548</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.3931087326111939</v>
+        <v>-0.3942041207943361</v>
       </c>
     </row>
     <row r="95">
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6167890581478948</v>
+        <v>0.6026551496397219</v>
       </c>
       <c r="C95" t="n">
-        <v>0.356990168900657</v>
+        <v>0.3374477108904962</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2597988892472377</v>
+        <v>0.2652074387492257</v>
       </c>
     </row>
     <row r="96">
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.3634009070858494</v>
+        <v>0.3378294437612975</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5458868946618374</v>
+        <v>0.5266494941439254</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.182485987575988</v>
+        <v>-0.1888200503826278</v>
       </c>
     </row>
     <row r="97">
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5071591067231968</v>
+        <v>0.487090270111473</v>
       </c>
       <c r="C97" t="n">
-        <v>0.4205728978473334</v>
+        <v>0.3997821350762529</v>
       </c>
       <c r="D97" t="n">
-        <v>0.08658620887586338</v>
+        <v>0.08730813503522017</v>
       </c>
     </row>
     <row r="98">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5175976554353918</v>
+        <v>0.5028030847682692</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4492004463163006</v>
+        <v>0.4328675057369059</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0683972091190912</v>
+        <v>0.06993557903136327</v>
       </c>
     </row>
     <row r="99">
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.2878496498803891</v>
+        <v>0.2685356517548581</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5113183385702268</v>
+        <v>0.4956755493221132</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.2234686886898377</v>
+        <v>-0.2271398975672552</v>
       </c>
     </row>
     <row r="100">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4140106070322898</v>
+        <v>0.395217709960718</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6586518588322354</v>
+        <v>0.6453499741801038</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.2446412517999456</v>
+        <v>-0.2501322642193858</v>
       </c>
     </row>
     <row r="101">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.461641286074791</v>
+        <v>0.4450228275820224</v>
       </c>
       <c r="C101" t="n">
-        <v>0.3417492188019414</v>
+        <v>0.3237096926974</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1198920672728496</v>
+        <v>0.1213131348846224</v>
       </c>
     </row>
     <row r="102">
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.285509875491462</v>
+        <v>0.2694488423388679</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6173683236833815</v>
+        <v>0.6047363467749574</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.3318584481919195</v>
+        <v>-0.3352875044360895</v>
       </c>
     </row>
     <row r="103">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4263514096665801</v>
+        <v>0.4061419487539444</v>
       </c>
       <c r="C103" t="n">
-        <v>0.5089574004966135</v>
+        <v>0.4919584009386831</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.08260599083003339</v>
+        <v>-0.08581645218473871</v>
       </c>
     </row>
     <row r="104">
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6055184152963267</v>
+        <v>0.588528196068828</v>
       </c>
       <c r="C104" t="n">
-        <v>0.4044929366976641</v>
+        <v>0.3810138205196368</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2010254785986626</v>
+        <v>0.2075143755491912</v>
       </c>
     </row>
     <row r="105">
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5780002568548658</v>
+        <v>0.5644639654209821</v>
       </c>
       <c r="C105" t="n">
-        <v>0.5589869573889338</v>
+        <v>0.5441772314348835</v>
       </c>
       <c r="D105" t="n">
-        <v>0.019013299465932</v>
+        <v>0.02028673398609859</v>
       </c>
     </row>
     <row r="106">
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.2300864180350107</v>
+        <v>0.2150758074774245</v>
       </c>
       <c r="C106" t="n">
-        <v>0.4811153860607094</v>
+        <v>0.4673783180094541</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.2510289680256986</v>
+        <v>-0.2523025105320296</v>
       </c>
     </row>
     <row r="107">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6077912917941478</v>
+        <v>0.5924878288544653</v>
       </c>
       <c r="C107" t="n">
-        <v>0.4277814553264555</v>
+        <v>0.4080414462808655</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1800098364676923</v>
+        <v>0.1844463825735997</v>
       </c>
     </row>
     <row r="108">
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.3661218342741022</v>
+        <v>0.3467679732014358</v>
       </c>
       <c r="C108" t="n">
-        <v>0.5979648381380747</v>
+        <v>0.5840239009738226</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.2318430038639725</v>
+        <v>-0.2372559277723868</v>
       </c>
     </row>
     <row r="109">
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7194075324547686</v>
+        <v>0.7091339574633032</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3870500342541979</v>
+        <v>0.3697737627075141</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3323574982005708</v>
+        <v>0.3393601947557891</v>
       </c>
     </row>
     <row r="110">
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.3849754769675103</v>
+        <v>0.3618456576958351</v>
       </c>
       <c r="C110" t="n">
-        <v>0.5520497596424845</v>
+        <v>0.533144191134456</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.1670742826749742</v>
+        <v>-0.1712985334386209</v>
       </c>
     </row>
     <row r="111">
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.3857611142380599</v>
+        <v>0.3660665450534274</v>
       </c>
       <c r="C111" t="n">
-        <v>0.5593500952469048</v>
+        <v>0.5419275392874932</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.173588981008845</v>
+        <v>-0.1758609942340658</v>
       </c>
     </row>
     <row r="112">
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.2378787834990158</v>
+        <v>0.2153582330547927</v>
       </c>
       <c r="C112" t="n">
-        <v>0.5322820522456011</v>
+        <v>0.5139251742461048</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.2944032687465853</v>
+        <v>-0.2985669411913121</v>
       </c>
     </row>
     <row r="113">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4844030870486096</v>
+        <v>0.4670114266682207</v>
       </c>
       <c r="C113" t="n">
-        <v>0.6114504412576638</v>
+        <v>0.5966145379766369</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.1270473542090542</v>
+        <v>-0.1296031113084162</v>
       </c>
     </row>
     <row r="114">
@@ -2331,13 +2331,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5235656080419525</v>
+        <v>0.503966398777058</v>
       </c>
       <c r="C114" t="n">
-        <v>0.5434703115831221</v>
+        <v>0.5250575218399656</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.01990470354116958</v>
+        <v>-0.02109112306290761</v>
       </c>
     </row>
     <row r="115">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.52841797637183</v>
+        <v>0.5158725793574404</v>
       </c>
       <c r="C115" t="n">
-        <v>0.5083836065478995</v>
+        <v>0.4944678198535142</v>
       </c>
       <c r="D115" t="n">
-        <v>0.02003436982393048</v>
+        <v>0.02140475950392612</v>
       </c>
     </row>
     <row r="116">
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.3201547240854294</v>
+        <v>0.3020713973605649</v>
       </c>
       <c r="C116" t="n">
-        <v>0.5038236067791516</v>
+        <v>0.4888393880226238</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.1836688826937222</v>
+        <v>-0.1867679906620589</v>
       </c>
     </row>
     <row r="117">
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.2313341462941253</v>
+        <v>0.2166784744129847</v>
       </c>
       <c r="C117" t="n">
-        <v>0.5404163402641476</v>
+        <v>0.5250216184338782</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.3090821939700223</v>
+        <v>-0.3083431440208935</v>
       </c>
     </row>
     <row r="118">
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6527256141701295</v>
+        <v>0.640057550213478</v>
       </c>
       <c r="C118" t="n">
-        <v>0.3646525583694423</v>
+        <v>0.3451004837029092</v>
       </c>
       <c r="D118" t="n">
-        <v>0.2880730558006872</v>
+        <v>0.2949570665105688</v>
       </c>
     </row>
     <row r="119">
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6685878474612457</v>
+        <v>0.6548157053065888</v>
       </c>
       <c r="C119" t="n">
-        <v>0.3824539013652538</v>
+        <v>0.3615755636834756</v>
       </c>
       <c r="D119" t="n">
-        <v>0.2861339460959919</v>
+        <v>0.2932401416231132</v>
       </c>
     </row>
     <row r="120">
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5562976724902244</v>
+        <v>0.5389596698894612</v>
       </c>
       <c r="C120" t="n">
-        <v>0.5712855875100812</v>
+        <v>0.5530873873626122</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.01498791501985675</v>
+        <v>-0.014127717473151</v>
       </c>
     </row>
     <row r="121">
@@ -2443,13 +2443,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.7446396000001653</v>
+        <v>0.7331868387061853</v>
       </c>
       <c r="C121" t="n">
-        <v>0.3024522826014691</v>
+        <v>0.2775608295367391</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4421873173986962</v>
+        <v>0.4556260091694462</v>
       </c>
     </row>
     <row r="122">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.6633318205600344</v>
+        <v>0.6519285912900302</v>
       </c>
       <c r="C122" t="n">
-        <v>0.4577531558667179</v>
+        <v>0.4405122575756186</v>
       </c>
       <c r="D122" t="n">
-        <v>0.2055786646933164</v>
+        <v>0.2114163337144117</v>
       </c>
     </row>
     <row r="123">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.7375853825630234</v>
+        <v>0.7286654103748402</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3907637963479533</v>
+        <v>0.3728797892852014</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3468215862150701</v>
+        <v>0.3557856210896388</v>
       </c>
     </row>
     <row r="124">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5354205750658345</v>
+        <v>0.5156610875610959</v>
       </c>
       <c r="C124" t="n">
-        <v>0.4330792934096079</v>
+        <v>0.4113353928138187</v>
       </c>
       <c r="D124" t="n">
-        <v>0.1023412816562266</v>
+        <v>0.1043256947472772</v>
       </c>
     </row>
     <row r="125">
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.2971887193637598</v>
+        <v>0.2810848197779969</v>
       </c>
       <c r="C125" t="n">
-        <v>0.573687717340718</v>
+        <v>0.5589770737654576</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.2764989979769582</v>
+        <v>-0.2778922539874607</v>
       </c>
     </row>
     <row r="126">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.3159641080425719</v>
+        <v>0.2906595706694708</v>
       </c>
       <c r="C126" t="n">
-        <v>0.5732497839239412</v>
+        <v>0.554996379103301</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.2572856758813694</v>
+        <v>-0.2643368084338302</v>
       </c>
     </row>
     <row r="127">
@@ -2539,13 +2539,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3718734011094313</v>
+        <v>0.3503657345749583</v>
       </c>
       <c r="C127" t="n">
-        <v>0.5647469380793946</v>
+        <v>0.54800361784109</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.1928735369699633</v>
+        <v>-0.1976378832661317</v>
       </c>
     </row>
     <row r="128">
@@ -2555,13 +2555,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.3773441619820937</v>
+        <v>0.3578467385084001</v>
       </c>
       <c r="C128" t="n">
-        <v>0.6316517460969003</v>
+        <v>0.616994686295899</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.2543075841148066</v>
+        <v>-0.2591479477874989</v>
       </c>
     </row>
     <row r="129">
@@ -2571,13 +2571,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4611928224344143</v>
+        <v>0.4436491130658278</v>
       </c>
       <c r="C129" t="n">
-        <v>0.4576256059524257</v>
+        <v>0.4408269853055761</v>
       </c>
       <c r="D129" t="n">
-        <v>0.003567216481988544</v>
+        <v>0.002822127760251703</v>
       </c>
     </row>
     <row r="130">
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4148941134398276</v>
+        <v>0.3982480010860507</v>
       </c>
       <c r="C130" t="n">
-        <v>0.62998600925586</v>
+        <v>0.6174430969208629</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.2150918958160324</v>
+        <v>-0.2191950958348121</v>
       </c>
     </row>
     <row r="131">
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6549654546723428</v>
+        <v>0.6401740998721446</v>
       </c>
       <c r="C131" t="n">
-        <v>0.5047999236868501</v>
+        <v>0.4853575215344046</v>
       </c>
       <c r="D131" t="n">
-        <v>0.1501655309854927</v>
+        <v>0.1548165783377399</v>
       </c>
     </row>
     <row r="132">
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.2599156508442142</v>
+        <v>0.2495821454653234</v>
       </c>
       <c r="C132" t="n">
-        <v>0.5413384574915522</v>
+        <v>0.5333703062025809</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.281422806647338</v>
+        <v>-0.2837881607372574</v>
       </c>
     </row>
     <row r="133">
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.3500442475866173</v>
+        <v>0.3326224677185819</v>
       </c>
       <c r="C133" t="n">
-        <v>0.6352563861676634</v>
+        <v>0.6215009457109943</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.2852121385810461</v>
+        <v>-0.2888784779924125</v>
       </c>
     </row>
     <row r="134">
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4022235702743764</v>
+        <v>0.3872696343614584</v>
       </c>
       <c r="C134" t="n">
-        <v>0.5027020347282644</v>
+        <v>0.4871511640342595</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.100478464453888</v>
+        <v>-0.09988152967280106</v>
       </c>
     </row>
     <row r="135">
@@ -2667,13 +2667,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.2948338723018367</v>
+        <v>0.271510068886523</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6666488409940365</v>
+        <v>0.6528514943455954</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.3718149686921999</v>
+        <v>-0.3813414254590725</v>
       </c>
     </row>
     <row r="136">
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.2886821569697072</v>
+        <v>0.2730153928487399</v>
       </c>
       <c r="C136" t="n">
-        <v>0.5247183061949512</v>
+        <v>0.5101492053888722</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.236036149225244</v>
+        <v>-0.2371338125401323</v>
       </c>
     </row>
     <row r="137">
@@ -2699,13 +2699,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.2847863871876499</v>
+        <v>0.2646222896202271</v>
       </c>
       <c r="C137" t="n">
-        <v>0.662593259583226</v>
+        <v>0.6486813519236586</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.3778068723955761</v>
+        <v>-0.3840590623034315</v>
       </c>
     </row>
     <row r="138">
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.3418742393978199</v>
+        <v>0.3263348973686405</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4218686315375653</v>
+        <v>0.4071858757528258</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.07999439213974546</v>
+        <v>-0.08085097838418537</v>
       </c>
     </row>
     <row r="139">
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.7370760088057445</v>
+        <v>0.7277413069014421</v>
       </c>
       <c r="C139" t="n">
-        <v>0.3653575155444683</v>
+        <v>0.3481675512654805</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3717184932612763</v>
+        <v>0.3795737556359616</v>
       </c>
     </row>
     <row r="140">
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4539754897689587</v>
+        <v>0.4394157850143329</v>
       </c>
       <c r="C140" t="n">
-        <v>0.4242891892595022</v>
+        <v>0.4099397433899539</v>
       </c>
       <c r="D140" t="n">
-        <v>0.02968630050945653</v>
+        <v>0.029476041624379</v>
       </c>
     </row>
     <row r="141">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3697372110434378</v>
+        <v>0.3536585898189726</v>
       </c>
       <c r="C141" t="n">
-        <v>0.5373674275820005</v>
+        <v>0.5241752147329245</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.1676302165385627</v>
+        <v>-0.1705166249139519</v>
       </c>
     </row>
     <row r="142">
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.2733893816528817</v>
+        <v>0.2585595247916839</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4705001980094987</v>
+        <v>0.4555523471660755</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.197110816356617</v>
+        <v>-0.1969928223743916</v>
       </c>
     </row>
     <row r="143">
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.3305722123504244</v>
+        <v>0.3121234780338815</v>
       </c>
       <c r="C143" t="n">
-        <v>0.5701900313057354</v>
+        <v>0.5552202024646543</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.239617818955311</v>
+        <v>-0.2430967244307728</v>
       </c>
     </row>
     <row r="144">
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.2600907416209359</v>
+        <v>0.2422277310487854</v>
       </c>
       <c r="C144" t="n">
-        <v>0.6004688633676646</v>
+        <v>0.5846044666892781</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.3403781217467287</v>
+        <v>-0.3423767356404927</v>
       </c>
     </row>
     <row r="145">
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.3837535580799645</v>
+        <v>0.3662978983084585</v>
       </c>
       <c r="C145" t="n">
-        <v>0.6500796373969121</v>
+        <v>0.6374878921492236</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.2663260793169476</v>
+        <v>-0.2711899938407651</v>
       </c>
     </row>
     <row r="146">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.3619134613836053</v>
+        <v>0.3376177337071652</v>
       </c>
       <c r="C146" t="n">
-        <v>0.5556450051019965</v>
+        <v>0.536930090721032</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.1937315437183912</v>
+        <v>-0.1993123570138668</v>
       </c>
     </row>
     <row r="147">
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4297020855211077</v>
+        <v>0.4098737204091548</v>
       </c>
       <c r="C147" t="n">
-        <v>0.5807806488352127</v>
+        <v>0.564211332031644</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.151078563314105</v>
+        <v>-0.1543376116224892</v>
       </c>
     </row>
     <row r="148">
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.2392530809163029</v>
+        <v>0.2310769406718586</v>
       </c>
       <c r="C148" t="n">
-        <v>0.5667609981991254</v>
+        <v>0.5595744453305711</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.3275079172828225</v>
+        <v>-0.3284975046587125</v>
       </c>
     </row>
     <row r="149">
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.3630709600797159</v>
+        <v>0.3421190823220358</v>
       </c>
       <c r="C149" t="n">
-        <v>0.6432952827488921</v>
+        <v>0.6288214210415348</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.2802243226691762</v>
+        <v>-0.286702338719499</v>
       </c>
     </row>
     <row r="150">
@@ -2907,13 +2907,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4051451911359469</v>
+        <v>0.3813050855374096</v>
       </c>
       <c r="C150" t="n">
-        <v>0.5328992059385506</v>
+        <v>0.5124905658071238</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.1277540148026037</v>
+        <v>-0.1311854802697142</v>
       </c>
     </row>
     <row r="151">
@@ -2923,13 +2923,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.2064373941041485</v>
+        <v>0.1959804336258424</v>
       </c>
       <c r="C151" t="n">
-        <v>0.562000098282087</v>
+        <v>0.5528528693696585</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.3555627041779385</v>
+        <v>-0.3568724357438161</v>
       </c>
     </row>
     <row r="152">
@@ -2939,13 +2939,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.2760425850501383</v>
+        <v>0.2582271181809174</v>
       </c>
       <c r="C152" t="n">
-        <v>0.539013652538135</v>
+        <v>0.5220943449843706</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.2629710674879968</v>
+        <v>-0.2638672268034532</v>
       </c>
     </row>
     <row r="153">
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5713145972437244</v>
+        <v>0.5586408476434052</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5208907247725783</v>
+        <v>0.5074602694436041</v>
       </c>
       <c r="D153" t="n">
-        <v>0.0504238724711461</v>
+        <v>0.05118057819980104</v>
       </c>
     </row>
     <row r="154">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.3219931772410071</v>
+        <v>0.3083554755859022</v>
       </c>
       <c r="C154" t="n">
-        <v>0.4776690090564052</v>
+        <v>0.4662867016839461</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.1556758318153981</v>
+        <v>-0.157931226098044</v>
       </c>
     </row>
     <row r="155">
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4959528840630641</v>
+        <v>0.4764240120233851</v>
       </c>
       <c r="C155" t="n">
-        <v>0.4713551076333384</v>
+        <v>0.45196658997088</v>
       </c>
       <c r="D155" t="n">
-        <v>0.02459777642972572</v>
+        <v>0.02445742205250506</v>
       </c>
     </row>
     <row r="156">
@@ -3003,13 +3003,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.3218756929816266</v>
+        <v>0.3046468392561949</v>
       </c>
       <c r="C156" t="n">
-        <v>0.5687273626001972</v>
+        <v>0.5533203775510516</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.2468516696185706</v>
+        <v>-0.2486735382948567</v>
       </c>
     </row>
     <row r="157">
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.3141927592530727</v>
+        <v>0.2948062503792229</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6172122286041342</v>
+        <v>0.6016135143476122</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.3030194693510615</v>
+        <v>-0.3068072639683894</v>
       </c>
     </row>
     <row r="158">
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.7438661447529961</v>
+        <v>0.7344095188332462</v>
       </c>
       <c r="C158" t="n">
-        <v>0.3651360195176662</v>
+        <v>0.3459995966596082</v>
       </c>
       <c r="D158" t="n">
-        <v>0.3787301252353299</v>
+        <v>0.388409922173638</v>
       </c>
     </row>
     <row r="159">
@@ -3051,13 +3051,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.3438295573878604</v>
+        <v>0.3263333695641261</v>
       </c>
       <c r="C159" t="n">
-        <v>0.4827052433493378</v>
+        <v>0.4651431400049501</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.1388756859614775</v>
+        <v>-0.1388097704408239</v>
       </c>
     </row>
     <row r="160">
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.2149074104280598</v>
+        <v>0.2029077175517238</v>
       </c>
       <c r="C160" t="n">
-        <v>0.4656706451640877</v>
+        <v>0.4514761647217714</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.2507632347360279</v>
+        <v>-0.2485684471700476</v>
       </c>
     </row>
     <row r="161">
@@ -3083,13 +3083,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.3816875695046376</v>
+        <v>0.3636654911302218</v>
       </c>
       <c r="C161" t="n">
-        <v>0.5555358830790044</v>
+        <v>0.5402973718706745</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.1738483135743668</v>
+        <v>-0.1766318807404527</v>
       </c>
     </row>
     <row r="162">
@@ -3099,13 +3099,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.3098747481521523</v>
+        <v>0.298102161232266</v>
       </c>
       <c r="C162" t="n">
-        <v>0.5478810815654601</v>
+        <v>0.5374892671732866</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.2380063334133078</v>
+        <v>-0.2393871059410206</v>
       </c>
     </row>
     <row r="163">
@@ -3115,13 +3115,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.2785074832724301</v>
+        <v>0.2608778590133264</v>
       </c>
       <c r="C163" t="n">
-        <v>0.5435758202940947</v>
+        <v>0.5278113894770936</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.2650683370216645</v>
+        <v>-0.2669335304637672</v>
       </c>
     </row>
     <row r="164">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.3923495241371308</v>
+        <v>0.3713804674121479</v>
       </c>
       <c r="C164" t="n">
-        <v>0.5669279332144312</v>
+        <v>0.5506948454931294</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.1745784090773005</v>
+        <v>-0.1793143780809815</v>
       </c>
     </row>
     <row r="165">
@@ -3147,13 +3147,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.3590839283597917</v>
+        <v>0.3344791867191009</v>
       </c>
       <c r="C165" t="n">
-        <v>0.5286391110674301</v>
+        <v>0.5097748932828546</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.1695551827076384</v>
+        <v>-0.1752957065637537</v>
       </c>
     </row>
     <row r="166">
@@ -3163,13 +3163,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.4520480459002124</v>
+        <v>0.4330893647781693</v>
       </c>
       <c r="C166" t="n">
-        <v>0.5553516041660043</v>
+        <v>0.5378819129334764</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.1033035582657919</v>
+        <v>-0.1047925481553071</v>
       </c>
     </row>
     <row r="167">
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.3249098427032364</v>
+        <v>0.3123369341503159</v>
       </c>
       <c r="C167" t="n">
-        <v>0.5197893872690009</v>
+        <v>0.5097260035383951</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.1948795445657645</v>
+        <v>-0.1973890693880793</v>
       </c>
     </row>
     <row r="168">
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.5618064247578358</v>
+        <v>0.5450189425934002</v>
       </c>
       <c r="C168" t="n">
-        <v>0.5078249885096678</v>
+        <v>0.4900906599198819</v>
       </c>
       <c r="D168" t="n">
-        <v>0.05398143624816798</v>
+        <v>0.05492828267351829</v>
       </c>
     </row>
     <row r="169">
@@ -3211,13 +3211,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.2317561811380157</v>
+        <v>0.223313074645473</v>
       </c>
       <c r="C169" t="n">
-        <v>0.4663990888672412</v>
+        <v>0.4582932284648316</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.2346429077292254</v>
+        <v>-0.2349801538193586</v>
       </c>
     </row>
     <row r="170">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.5494375415272789</v>
+        <v>0.5346006253522135</v>
       </c>
       <c r="C170" t="n">
-        <v>0.4873982130004076</v>
+        <v>0.472413961688774</v>
       </c>
       <c r="D170" t="n">
-        <v>0.06203932852687122</v>
+        <v>0.0621866636634395</v>
       </c>
     </row>
     <row r="171">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.397370582519581</v>
+        <v>0.3756674868794331</v>
       </c>
       <c r="C171" t="n">
-        <v>0.5013716132426441</v>
+        <v>0.4824760822203277</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.1040010307230631</v>
+        <v>-0.1068085953408946</v>
       </c>
     </row>
     <row r="172">
@@ -3259,13 +3259,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.5129348311303141</v>
+        <v>0.4987777563885146</v>
       </c>
       <c r="C172" t="n">
-        <v>0.3313298722621935</v>
+        <v>0.316639777307214</v>
       </c>
       <c r="D172" t="n">
-        <v>0.1816049588681206</v>
+        <v>0.1821379790813006</v>
       </c>
     </row>
     <row r="173">
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.3849895172656437</v>
+        <v>0.3731151803093062</v>
       </c>
       <c r="C173" t="n">
-        <v>0.4832660293747814</v>
+        <v>0.4728745947498526</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.09827651210913763</v>
+        <v>-0.09975941444054637</v>
       </c>
     </row>
     <row r="174">
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.411566356307253</v>
+        <v>0.3927444127097622</v>
       </c>
       <c r="C174" t="n">
-        <v>0.587608363227468</v>
+        <v>0.5742597023225684</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.176042006920215</v>
+        <v>-0.1815152896128062</v>
       </c>
     </row>
     <row r="175">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.3616904684132522</v>
+        <v>0.3461594704891463</v>
       </c>
       <c r="C175" t="n">
-        <v>0.385241932919585</v>
+        <v>0.3706125273858959</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.02355146450633283</v>
+        <v>-0.02445305689674959</v>
       </c>
     </row>
     <row r="176">
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.2260925726409924</v>
+        <v>0.2082480491027641</v>
       </c>
       <c r="C176" t="n">
-        <v>0.5724382340443368</v>
+        <v>0.5553011761039152</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.3463456614033443</v>
+        <v>-0.3470531270011511</v>
       </c>
     </row>
     <row r="177">
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.3208179216972573</v>
+        <v>0.3020002453217534</v>
       </c>
       <c r="C177" t="n">
-        <v>0.5862251873863614</v>
+        <v>0.5702981052168413</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.2654072656891041</v>
+        <v>-0.2682978598950879</v>
       </c>
     </row>
     <row r="178">
@@ -3355,13 +3355,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.7051739737471202</v>
+        <v>0.6952676036910012</v>
       </c>
       <c r="C178" t="n">
-        <v>0.3302046868992869</v>
+        <v>0.3129134620966978</v>
       </c>
       <c r="D178" t="n">
-        <v>0.3749692868478333</v>
+        <v>0.3823541415943033</v>
       </c>
     </row>
     <row r="179">
@@ -3371,13 +3371,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.322209356537266</v>
+        <v>0.3060753364771185</v>
       </c>
       <c r="C179" t="n">
-        <v>0.5020126147949228</v>
+        <v>0.4875827688095652</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.1798032582576568</v>
+        <v>-0.1815074323324468</v>
       </c>
     </row>
     <row r="180">
@@ -3387,13 +3387,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.2935745814442594</v>
+        <v>0.279848171152519</v>
       </c>
       <c r="C180" t="n">
-        <v>0.6584292788118273</v>
+        <v>0.6474102185677139</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.3648546973675679</v>
+        <v>-0.3675620474151949</v>
       </c>
     </row>
     <row r="181">
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.724668514755321</v>
+        <v>0.7142381340879814</v>
       </c>
       <c r="C181" t="n">
-        <v>0.3923724428590837</v>
+        <v>0.3737682076102998</v>
       </c>
       <c r="D181" t="n">
-        <v>0.3322960718962373</v>
+        <v>0.3404699264776816</v>
       </c>
     </row>
     <row r="182">
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.4274234277240552</v>
+        <v>0.4112568200102232</v>
       </c>
       <c r="C182" t="n">
-        <v>0.4788791072517727</v>
+        <v>0.4634854721068729</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.05145567952771751</v>
+        <v>-0.05222865209664967</v>
       </c>
     </row>
     <row r="183">
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.5050584303524818</v>
+        <v>0.4887167271458996</v>
       </c>
       <c r="C183" t="n">
-        <v>0.4308813157080791</v>
+        <v>0.4138600897737933</v>
       </c>
       <c r="D183" t="n">
-        <v>0.07417711464440269</v>
+        <v>0.07485663737210629</v>
       </c>
     </row>
     <row r="184">
@@ -3451,13 +3451,13 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.7119261182994225</v>
+        <v>0.6989592159132626</v>
       </c>
       <c r="C184" t="n">
-        <v>0.4073091520857481</v>
+        <v>0.3856728603861678</v>
       </c>
       <c r="D184" t="n">
-        <v>0.3046169662136744</v>
+        <v>0.3132863555270948</v>
       </c>
     </row>
     <row r="185">
@@ -3467,13 +3467,13 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.569415027496272</v>
+        <v>0.5613354582911551</v>
       </c>
       <c r="C185" t="n">
-        <v>0.4003509971295849</v>
+        <v>0.3907337128399747</v>
       </c>
       <c r="D185" t="n">
-        <v>0.1690640303666871</v>
+        <v>0.1706017454511804</v>
       </c>
     </row>
     <row r="186">
@@ -3483,13 +3483,13 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.7017931525466004</v>
+        <v>0.691173087592525</v>
       </c>
       <c r="C186" t="n">
-        <v>0.4542695617486117</v>
+        <v>0.4359135659874048</v>
       </c>
       <c r="D186" t="n">
-        <v>0.2475235907979886</v>
+        <v>0.2552595216051203</v>
       </c>
     </row>
     <row r="187">
@@ -3499,13 +3499,13 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.5834099011356536</v>
+        <v>0.5690547997288365</v>
       </c>
       <c r="C187" t="n">
-        <v>0.5096410391307239</v>
+        <v>0.495627423479911</v>
       </c>
       <c r="D187" t="n">
-        <v>0.07376886200492971</v>
+        <v>0.07342737624892559</v>
       </c>
     </row>
     <row r="188">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.5279721969060965</v>
+        <v>0.5117210979763573</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3508229679455864</v>
+        <v>0.3317711532174035</v>
       </c>
       <c r="D188" t="n">
-        <v>0.1771492289605101</v>
+        <v>0.1799499447589538</v>
       </c>
     </row>
     <row r="189">
@@ -3531,13 +3531,13 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.2679799438470665</v>
+        <v>0.2425863285940837</v>
       </c>
       <c r="C189" t="n">
-        <v>0.49975863075709</v>
+        <v>0.4789040752657616</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.2317786869100235</v>
+        <v>-0.2363177466716778</v>
       </c>
     </row>
     <row r="190">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.2824445480489973</v>
+        <v>0.2676401400516573</v>
       </c>
       <c r="C190" t="n">
-        <v>0.464796946317746</v>
+        <v>0.4497982534138792</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.1823523982687487</v>
+        <v>-0.182158113362222</v>
       </c>
     </row>
     <row r="191">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.5384289154158757</v>
+        <v>0.5207364541577891</v>
       </c>
       <c r="C191" t="n">
-        <v>0.6280391567396942</v>
+        <v>0.6127932238814179</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.08961024132381856</v>
+        <v>-0.09205676972362875</v>
       </c>
     </row>
     <row r="192">
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.3765657513355834</v>
+        <v>0.3579790027277858</v>
       </c>
       <c r="C192" t="n">
-        <v>0.5092302055540943</v>
+        <v>0.4932440484375144</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.1326644542185109</v>
+        <v>-0.1352650457097286</v>
       </c>
     </row>
     <row r="193">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2636435564735892</v>
+        <v>0.2457170183017886</v>
       </c>
       <c r="C193" t="n">
-        <v>0.5545039211662037</v>
+        <v>0.5387749146721179</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2908603646926146</v>
+        <v>-0.2930578963703293</v>
       </c>
     </row>
     <row r="194">
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.3548012244791772</v>
+        <v>0.3384152476636595</v>
       </c>
       <c r="C194" t="n">
-        <v>0.7053849911690655</v>
+        <v>0.6939670055337078</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.3505837666898883</v>
+        <v>-0.3555517578700483</v>
       </c>
     </row>
     <row r="195">
@@ -3627,13 +3627,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.6418010233725538</v>
+        <v>0.6307558398144983</v>
       </c>
       <c r="C195" t="n">
-        <v>0.3846327285130787</v>
+        <v>0.3688662468259861</v>
       </c>
       <c r="D195" t="n">
-        <v>0.2571682948594752</v>
+        <v>0.2618895929885123</v>
       </c>
     </row>
     <row r="196">
@@ -3643,13 +3643,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.6970260583803856</v>
+        <v>0.6882768067488799</v>
       </c>
       <c r="C196" t="n">
-        <v>0.3489816241403931</v>
+        <v>0.3320931380188042</v>
       </c>
       <c r="D196" t="n">
-        <v>0.3480444342399925</v>
+        <v>0.3561836687300757</v>
       </c>
     </row>
     <row r="197">
@@ -3659,13 +3659,13 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.2605288815126852</v>
+        <v>0.2392847430385587</v>
       </c>
       <c r="C197" t="n">
-        <v>0.6321446018563751</v>
+        <v>0.617110035536733</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.3716157203436899</v>
+        <v>-0.3778252924981743</v>
       </c>
     </row>
     <row r="198">
@@ -3675,13 +3675,13 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.2200620581177494</v>
+        <v>0.2048307869197235</v>
       </c>
       <c r="C198" t="n">
-        <v>0.6013573767932867</v>
+        <v>0.5874167728490803</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.3812953186755373</v>
+        <v>-0.3825859859293569</v>
       </c>
     </row>
     <row r="199">
@@ -3691,13 +3691,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.4901732366314681</v>
+        <v>0.4725839845054431</v>
       </c>
       <c r="C199" t="n">
-        <v>0.4899231954397112</v>
+        <v>0.4719938154473259</v>
       </c>
       <c r="D199" t="n">
-        <v>0.0002500411917568668</v>
+        <v>0.000590169058117207</v>
       </c>
     </row>
     <row r="200">
@@ -3707,13 +3707,13 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.3511689167620925</v>
+        <v>0.3353199157175726</v>
       </c>
       <c r="C200" t="n">
-        <v>0.3834027571016035</v>
+        <v>0.3679258831473995</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.03223384033951104</v>
+        <v>-0.03260596742982691</v>
       </c>
     </row>
     <row r="201">
@@ -3723,13 +3723,13 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.2843476278709829</v>
+        <v>0.2681894949034624</v>
       </c>
       <c r="C201" t="n">
-        <v>0.5198414189620834</v>
+        <v>0.5037247874060019</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.2354937910911005</v>
+        <v>-0.2355352925025395</v>
       </c>
     </row>
     <row r="202">
@@ -3739,13 +3739,13 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.7310812144527524</v>
+        <v>0.7203790352045446</v>
       </c>
       <c r="C202" t="n">
-        <v>0.3232281040518236</v>
+        <v>0.3054356229011786</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4078531104009289</v>
+        <v>0.414943412303366</v>
       </c>
     </row>
     <row r="203">
@@ -3755,13 +3755,13 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.3010200689543818</v>
+        <v>0.2845583924702809</v>
       </c>
       <c r="C203" t="n">
-        <v>0.5054756130345173</v>
+        <v>0.4889509177521717</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.2044555440801354</v>
+        <v>-0.2043925252818908</v>
       </c>
     </row>
     <row r="204">
@@ -3771,13 +3771,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.2927315441313412</v>
+        <v>0.2807292778417274</v>
       </c>
       <c r="C204" t="n">
-        <v>0.4759136620772786</v>
+        <v>0.4631967170536596</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.1831821179459374</v>
+        <v>-0.1824674392119323</v>
       </c>
     </row>
     <row r="205">
@@ -3787,13 +3787,13 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5933202868680679</v>
+        <v>0.5800641590592914</v>
       </c>
       <c r="C205" t="n">
-        <v>0.3684754424861899</v>
+        <v>0.351754072362933</v>
       </c>
       <c r="D205" t="n">
-        <v>0.2248448443818781</v>
+        <v>0.2283100866963584</v>
       </c>
     </row>
     <row r="206">
@@ -3803,13 +3803,13 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.6764561957151488</v>
+        <v>0.6630496986078209</v>
       </c>
       <c r="C206" t="n">
-        <v>0.3731684121372596</v>
+        <v>0.3522360946872125</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3032877835778892</v>
+        <v>0.3108136039206084</v>
       </c>
     </row>
     <row r="207">
@@ -3819,13 +3819,13 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.3681737825512956</v>
+        <v>0.3527840308633973</v>
       </c>
       <c r="C207" t="n">
-        <v>0.5516985457141784</v>
+        <v>0.5392355477331965</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.1835247631628829</v>
+        <v>-0.1864515168697992</v>
       </c>
     </row>
   </sheetData>

--- a/results/GSE186332/glass_recurrence_score_gse186332_universe.xlsx
+++ b/results/GSE186332/glass_recurrence_score_gse186332_universe.xlsx
@@ -574,10 +574,10 @@
         <v>0.321586044422444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5835212532885993</v>
+        <v>0.5835212532885992</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2619352088661552</v>
+        <v>-0.2619352088661551</v>
       </c>
     </row>
     <row r="5">
@@ -590,10 +590,10 @@
         <v>0.3679935430616068</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6051091310764606</v>
+        <v>0.6051091310764605</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2371155880148538</v>
+        <v>-0.2371155880148537</v>
       </c>
     </row>
     <row r="6">
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2897219352132314</v>
+        <v>0.2897219352132313</v>
       </c>
       <c r="C6" t="n">
         <v>0.4486436151521541</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1589216799389228</v>
+        <v>-0.1589216799389229</v>
       </c>
     </row>
     <row r="7">
@@ -622,10 +622,10 @@
         <v>0.4381573106100786</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4439456162705068</v>
+        <v>0.4439456162705069</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.005788305660428261</v>
+        <v>-0.005788305660428372</v>
       </c>
     </row>
     <row r="8">
@@ -638,10 +638,10 @@
         <v>0.3242957148575497</v>
       </c>
       <c r="C8" t="n">
-        <v>0.497803017108355</v>
+        <v>0.4978030171083549</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1735073022508053</v>
+        <v>-0.1735073022508052</v>
       </c>
     </row>
     <row r="9">
@@ -654,10 +654,10 @@
         <v>0.7541570469546709</v>
       </c>
       <c r="C9" t="n">
-        <v>0.293325098467001</v>
+        <v>0.2933250984670009</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4608319484876699</v>
+        <v>0.46083194848767</v>
       </c>
     </row>
     <row r="10">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3139175570493119</v>
+        <v>0.3139175570493118</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5388322073414064</v>
+        <v>0.5388322073414062</v>
       </c>
       <c r="D12" t="n">
         <v>-0.2249146502920945</v>
@@ -718,10 +718,10 @@
         <v>0.2518140496030109</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5261689996241601</v>
+        <v>0.52616899962416</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2743549500211492</v>
+        <v>-0.2743549500211491</v>
       </c>
     </row>
     <row r="14">
@@ -734,10 +734,10 @@
         <v>0.2761733647799154</v>
       </c>
       <c r="C14" t="n">
-        <v>0.604905933076051</v>
+        <v>0.6049059330760511</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3287325682961356</v>
+        <v>-0.3287325682961357</v>
       </c>
     </row>
     <row r="15">
@@ -750,10 +750,10 @@
         <v>0.4126455943137735</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5640593154824654</v>
+        <v>0.5640593154824655</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1514137211686918</v>
+        <v>-0.151413721168692</v>
       </c>
     </row>
     <row r="16">
@@ -766,10 +766,10 @@
         <v>0.4155030252711962</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5398168773509092</v>
+        <v>0.5398168773509091</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.124313852079713</v>
+        <v>-0.1243138520797129</v>
       </c>
     </row>
     <row r="17">
@@ -798,10 +798,10 @@
         <v>0.5733911454561567</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4694484931264074</v>
+        <v>0.4694484931264075</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1039426523297493</v>
+        <v>0.1039426523297491</v>
       </c>
     </row>
     <row r="19">
@@ -846,10 +846,10 @@
         <v>0.4228836306222661</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4587378195785092</v>
+        <v>0.4587378195785093</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.03585418895624315</v>
+        <v>-0.0358541889562432</v>
       </c>
     </row>
     <row r="22">
@@ -878,10 +878,10 @@
         <v>0.3299320039687996</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5763291135372647</v>
+        <v>0.5763291135372646</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2463971095684651</v>
+        <v>-0.2463971095684649</v>
       </c>
     </row>
     <row r="24">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5968521115786193</v>
+        <v>0.5968521115786194</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4737920413607237</v>
+        <v>0.4737920413607238</v>
       </c>
       <c r="D24" t="n">
         <v>0.1230600702178956</v>
@@ -910,10 +910,10 @@
         <v>0.3818247573300787</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6558146712011905</v>
+        <v>0.6558146712011904</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2739899138711118</v>
+        <v>-0.2739899138711117</v>
       </c>
     </row>
     <row r="26">
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5203387884684808</v>
+        <v>0.5203387884684807</v>
       </c>
       <c r="C26" t="n">
         <v>0.5626781802014869</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04233939173300605</v>
+        <v>-0.04233939173300616</v>
       </c>
     </row>
     <row r="27">
@@ -974,10 +974,10 @@
         <v>0.5380892578318534</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5181923322547033</v>
+        <v>0.5181923322547034</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01989692557715006</v>
+        <v>0.01989692557714995</v>
       </c>
     </row>
     <row r="30">
@@ -990,10 +990,10 @@
         <v>0.21300475932932</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5413714184442672</v>
+        <v>0.5413714184442673</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3283666591149472</v>
+        <v>-0.3283666591149473</v>
       </c>
     </row>
     <row r="31">
@@ -1006,10 +1006,10 @@
         <v>0.6848981761942738</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3837699798635366</v>
+        <v>0.3837699798635364</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3011281963307373</v>
+        <v>0.3011281963307374</v>
       </c>
     </row>
     <row r="32">
@@ -1022,7 +1022,7 @@
         <v>0.6906195858427522</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3694720213159286</v>
+        <v>0.3694720213159285</v>
       </c>
       <c r="D32" t="n">
         <v>0.3211475645268236</v>
@@ -1057,7 +1057,7 @@
         <v>0.423421090424638</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03959141705614766</v>
+        <v>0.03959141705614772</v>
       </c>
     </row>
     <row r="35">
@@ -1073,7 +1073,7 @@
         <v>0.3756771993509886</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3169304966805173</v>
+        <v>0.3169304966805174</v>
       </c>
     </row>
     <row r="36">
@@ -1102,10 +1102,10 @@
         <v>0.2299166822720985</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4833354722596535</v>
+        <v>0.4833354722596533</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.253418789987555</v>
+        <v>-0.2534187899875548</v>
       </c>
     </row>
     <row r="38">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5802619006150067</v>
+        <v>0.5802619006150068</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4882343774349385</v>
+        <v>0.4882343774349384</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09202752318006818</v>
+        <v>0.09202752318006846</v>
       </c>
     </row>
     <row r="39">
@@ -1182,10 +1182,10 @@
         <v>0.2076037521132811</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6198241802564878</v>
+        <v>0.6198241802564879</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4122204281432067</v>
+        <v>-0.4122204281432068</v>
       </c>
     </row>
     <row r="43">
@@ -1214,10 +1214,10 @@
         <v>0.5195967119900788</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3175201746586121</v>
+        <v>0.317520174658612</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2020765373314667</v>
+        <v>0.2020765373314668</v>
       </c>
     </row>
     <row r="45">
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2610238734733413</v>
+        <v>0.2610238734733414</v>
       </c>
       <c r="C46" t="n">
         <v>0.5738410838856346</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3128172104122933</v>
+        <v>-0.3128172104122932</v>
       </c>
     </row>
     <row r="47">
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4909150195842713</v>
+        <v>0.4909150195842714</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6150467355400941</v>
+        <v>0.615046735540094</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1241317159558229</v>
+        <v>-0.1241317159558227</v>
       </c>
     </row>
     <row r="48">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.630228965514833</v>
+        <v>0.6302289655148331</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3412863197328175</v>
+        <v>0.3412863197328176</v>
       </c>
       <c r="D49" t="n">
         <v>0.2889426457820155</v>
@@ -1310,10 +1310,10 @@
         <v>0.5916228732415516</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3721601933589393</v>
+        <v>0.3721601933589394</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2194626798826123</v>
+        <v>0.2194626798826122</v>
       </c>
     </row>
     <row r="51">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4523353365033094</v>
+        <v>0.4523353365033095</v>
       </c>
       <c r="C51" t="n">
         <v>0.465768012051322</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.01343267554801264</v>
+        <v>-0.01343267554801253</v>
       </c>
     </row>
     <row r="52">
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3449088533652513</v>
+        <v>0.3449088533652514</v>
       </c>
       <c r="C52" t="n">
         <v>0.602559225341999</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2576503719767477</v>
+        <v>-0.2576503719767476</v>
       </c>
     </row>
     <row r="53">
@@ -1358,10 +1358,10 @@
         <v>0.5184910180372602</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5152268636923367</v>
+        <v>0.5152268636923369</v>
       </c>
       <c r="D53" t="n">
-        <v>0.003264154344923442</v>
+        <v>0.00326415434492322</v>
       </c>
     </row>
     <row r="54">
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2522558033654477</v>
+        <v>0.2522558033654478</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4320677000736403</v>
+        <v>0.4320677000736401</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.1798118967081925</v>
+        <v>-0.1798118967081923</v>
       </c>
     </row>
     <row r="59">
@@ -1454,10 +1454,10 @@
         <v>0.2383161149764566</v>
       </c>
       <c r="C59" t="n">
-        <v>0.6466256909495917</v>
+        <v>0.6466256909495918</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4083095759731351</v>
+        <v>-0.4083095759731352</v>
       </c>
     </row>
     <row r="60">
@@ -1489,7 +1489,7 @@
         <v>0.4959123590218384</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.2768457078951262</v>
+        <v>-0.2768457078951263</v>
       </c>
     </row>
     <row r="62">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5559959997712658</v>
+        <v>0.5559959997712659</v>
       </c>
       <c r="C62" t="n">
         <v>0.3876124082171438</v>
       </c>
       <c r="D62" t="n">
-        <v>0.168383591554122</v>
+        <v>0.1683835915541221</v>
       </c>
     </row>
     <row r="63">
@@ -1518,7 +1518,7 @@
         <v>0.2111454212353478</v>
       </c>
       <c r="C63" t="n">
-        <v>0.596718428683613</v>
+        <v>0.5967184286836131</v>
       </c>
       <c r="D63" t="n">
         <v>-0.3855730074482653</v>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4236920574681485</v>
+        <v>0.4236920574681486</v>
       </c>
       <c r="C65" t="n">
         <v>0.424709793532498</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.001017736064349517</v>
+        <v>-0.001017736064349462</v>
       </c>
     </row>
     <row r="66">
@@ -1566,10 +1566,10 @@
         <v>0.2531877641192054</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6337084857318337</v>
+        <v>0.6337084857318336</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.3805207216126283</v>
+        <v>-0.3805207216126282</v>
       </c>
     </row>
     <row r="67">
@@ -1582,10 +1582,10 @@
         <v>0.2324478178368121</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5449778010004064</v>
+        <v>0.5449778010004065</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.3125299831635943</v>
+        <v>-0.3125299831635944</v>
       </c>
     </row>
     <row r="68">
@@ -1598,10 +1598,10 @@
         <v>0.215393372558623</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4741785759028561</v>
+        <v>0.4741785759028559</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.2587852033442331</v>
+        <v>-0.258785203344233</v>
       </c>
     </row>
     <row r="69">
@@ -1614,10 +1614,10 @@
         <v>0.3953477916022261</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4541284333586949</v>
+        <v>0.4541284333586948</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.05878064175646885</v>
+        <v>-0.0587806417564688</v>
       </c>
     </row>
     <row r="70">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.2633352234457753</v>
+        <v>0.2633352234457754</v>
       </c>
       <c r="C72" t="n">
         <v>0.4891495323390382</v>
@@ -1694,10 +1694,10 @@
         <v>0.4612053329980894</v>
       </c>
       <c r="C74" t="n">
-        <v>0.49545707327656</v>
+        <v>0.4954570732765602</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.03425174027847067</v>
+        <v>-0.03425174027847083</v>
       </c>
     </row>
     <row r="75">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4190361823395402</v>
+        <v>0.4190361823395401</v>
       </c>
       <c r="C75" t="n">
         <v>0.6042906098078938</v>
@@ -1726,10 +1726,10 @@
         <v>0.359454425373079</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6227556551684099</v>
+        <v>0.6227556551684098</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.2633012297953309</v>
+        <v>-0.2633012297953308</v>
       </c>
     </row>
     <row r="77">
@@ -1742,10 +1742,10 @@
         <v>0.4211855850334524</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5783740798797311</v>
+        <v>0.5783740798797312</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.1571884948462787</v>
+        <v>-0.1571884948462788</v>
       </c>
     </row>
     <row r="78">
@@ -1761,7 +1761,7 @@
         <v>0.3860021022590118</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.04938748134441556</v>
+        <v>-0.04938748134441562</v>
       </c>
     </row>
     <row r="79">
@@ -1790,10 +1790,10 @@
         <v>0.2068402863716782</v>
       </c>
       <c r="C80" t="n">
-        <v>0.5344313664378016</v>
+        <v>0.5344313664378015</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.3275910800661235</v>
+        <v>-0.3275910800661234</v>
       </c>
     </row>
     <row r="81">
@@ -1806,10 +1806,10 @@
         <v>0.249440277903276</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3774387579560419</v>
+        <v>0.377438757956042</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.1279984800527659</v>
+        <v>-0.127998480052766</v>
       </c>
     </row>
     <row r="82">
@@ -1841,7 +1841,7 @@
         <v>0.354916245756523</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1966478113763815</v>
+        <v>0.1966478113763816</v>
       </c>
     </row>
     <row r="84">
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5674139376804174</v>
+        <v>0.5674139376804173</v>
       </c>
       <c r="C84" t="n">
         <v>0.3701083518961581</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1973055857842592</v>
+        <v>0.1973055857842591</v>
       </c>
     </row>
     <row r="85">
@@ -1873,7 +1873,7 @@
         <v>0.4252613309621807</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.1924795787100878</v>
+        <v>-0.1924795787100877</v>
       </c>
     </row>
     <row r="86">
@@ -1886,10 +1886,10 @@
         <v>0.2070668379553785</v>
       </c>
       <c r="C86" t="n">
-        <v>0.5935192060305499</v>
+        <v>0.59351920603055</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.3864523680751714</v>
+        <v>-0.3864523680751715</v>
       </c>
     </row>
     <row r="87">
@@ -1899,13 +1899,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5148731769472633</v>
+        <v>0.5148731769472632</v>
       </c>
       <c r="C87" t="n">
         <v>0.5051700904765833</v>
       </c>
       <c r="D87" t="n">
-        <v>0.009703086470679967</v>
+        <v>0.009703086470679856</v>
       </c>
     </row>
     <row r="88">
@@ -1921,7 +1921,7 @@
         <v>0.2849576950929975</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4562632127808268</v>
+        <v>0.4562632127808269</v>
       </c>
     </row>
     <row r="89">
@@ -1966,10 +1966,10 @@
         <v>0.7205379268740377</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4011392074361301</v>
+        <v>0.40113920743613</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3193987194379076</v>
+        <v>0.3193987194379077</v>
       </c>
     </row>
     <row r="92">
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.2672119182720619</v>
+        <v>0.2672119182720618</v>
       </c>
       <c r="C93" t="n">
-        <v>0.5698878897047364</v>
+        <v>0.5698878897047365</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.3026759714326745</v>
+        <v>-0.3026759714326747</v>
       </c>
     </row>
     <row r="94">
@@ -2014,10 +2014,10 @@
         <v>0.2000339172602187</v>
       </c>
       <c r="C94" t="n">
-        <v>0.5942380380545548</v>
+        <v>0.5942380380545549</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.3942041207943361</v>
+        <v>-0.3942041207943362</v>
       </c>
     </row>
     <row r="95">
@@ -2030,10 +2030,10 @@
         <v>0.6026551496397219</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3374477108904962</v>
+        <v>0.3374477108904961</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2652074387492257</v>
+        <v>0.2652074387492258</v>
       </c>
     </row>
     <row r="96">
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.3378294437612975</v>
+        <v>0.3378294437612976</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5266494941439254</v>
+        <v>0.5266494941439253</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.1888200503826278</v>
+        <v>-0.1888200503826277</v>
       </c>
     </row>
     <row r="97">
@@ -2062,10 +2062,10 @@
         <v>0.487090270111473</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3997821350762529</v>
+        <v>0.3997821350762527</v>
       </c>
       <c r="D97" t="n">
-        <v>0.08730813503522017</v>
+        <v>0.08730813503522034</v>
       </c>
     </row>
     <row r="98">
@@ -2094,10 +2094,10 @@
         <v>0.2685356517548581</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4956755493221132</v>
+        <v>0.4956755493221131</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.2271398975672552</v>
+        <v>-0.227139897567255</v>
       </c>
     </row>
     <row r="100">
@@ -2110,10 +2110,10 @@
         <v>0.395217709960718</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6453499741801038</v>
+        <v>0.6453499741801035</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.2501322642193858</v>
+        <v>-0.2501322642193855</v>
       </c>
     </row>
     <row r="101">
@@ -2129,7 +2129,7 @@
         <v>0.3237096926974</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1213131348846224</v>
+        <v>0.1213131348846225</v>
       </c>
     </row>
     <row r="102">
@@ -2142,10 +2142,10 @@
         <v>0.2694488423388679</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6047363467749574</v>
+        <v>0.6047363467749575</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.3352875044360895</v>
+        <v>-0.3352875044360896</v>
       </c>
     </row>
     <row r="103">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4061419487539444</v>
+        <v>0.4061419487539445</v>
       </c>
       <c r="C103" t="n">
         <v>0.4919584009386831</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.08581645218473871</v>
+        <v>-0.08581645218473866</v>
       </c>
     </row>
     <row r="104">
@@ -2190,10 +2190,10 @@
         <v>0.5644639654209821</v>
       </c>
       <c r="C105" t="n">
-        <v>0.5441772314348835</v>
+        <v>0.5441772314348834</v>
       </c>
       <c r="D105" t="n">
-        <v>0.02028673398609859</v>
+        <v>0.0202867339860987</v>
       </c>
     </row>
     <row r="106">
@@ -2225,7 +2225,7 @@
         <v>0.4080414462808655</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1844463825735997</v>
+        <v>0.1844463825735998</v>
       </c>
     </row>
     <row r="108">
@@ -2257,7 +2257,7 @@
         <v>0.3697737627075141</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3393601947557891</v>
+        <v>0.3393601947557892</v>
       </c>
     </row>
     <row r="110">
@@ -2270,10 +2270,10 @@
         <v>0.3618456576958351</v>
       </c>
       <c r="C110" t="n">
-        <v>0.533144191134456</v>
+        <v>0.5331441911344559</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.1712985334386209</v>
+        <v>-0.1712985334386208</v>
       </c>
     </row>
     <row r="111">
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.3660665450534274</v>
+        <v>0.3660665450534273</v>
       </c>
       <c r="C111" t="n">
         <v>0.5419275392874932</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4670114266682207</v>
+        <v>0.4670114266682206</v>
       </c>
       <c r="C113" t="n">
         <v>0.5966145379766369</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.1296031113084162</v>
+        <v>-0.1296031113084163</v>
       </c>
     </row>
     <row r="114">
@@ -2334,10 +2334,10 @@
         <v>0.503966398777058</v>
       </c>
       <c r="C114" t="n">
-        <v>0.5250575218399656</v>
+        <v>0.5250575218399655</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.02109112306290761</v>
+        <v>-0.0210911230629075</v>
       </c>
     </row>
     <row r="115">
@@ -2350,10 +2350,10 @@
         <v>0.5158725793574404</v>
       </c>
       <c r="C115" t="n">
-        <v>0.4944678198535142</v>
+        <v>0.4944678198535141</v>
       </c>
       <c r="D115" t="n">
-        <v>0.02140475950392612</v>
+        <v>0.02140475950392623</v>
       </c>
     </row>
     <row r="116">
@@ -2366,10 +2366,10 @@
         <v>0.3020713973605649</v>
       </c>
       <c r="C116" t="n">
-        <v>0.4888393880226238</v>
+        <v>0.4888393880226237</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.1867679906620589</v>
+        <v>-0.1867679906620588</v>
       </c>
     </row>
     <row r="117">
@@ -2382,10 +2382,10 @@
         <v>0.2166784744129847</v>
       </c>
       <c r="C117" t="n">
-        <v>0.5250216184338782</v>
+        <v>0.5250216184338781</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.3083431440208935</v>
+        <v>-0.3083431440208934</v>
       </c>
     </row>
     <row r="118">
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6548157053065888</v>
+        <v>0.6548157053065889</v>
       </c>
       <c r="C119" t="n">
-        <v>0.3615755636834756</v>
+        <v>0.3615755636834755</v>
       </c>
       <c r="D119" t="n">
-        <v>0.2932401416231132</v>
+        <v>0.2932401416231134</v>
       </c>
     </row>
     <row r="120">
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5389596698894612</v>
+        <v>0.5389596698894611</v>
       </c>
       <c r="C120" t="n">
-        <v>0.5530873873626122</v>
+        <v>0.5530873873626121</v>
       </c>
       <c r="D120" t="n">
         <v>-0.014127717473151</v>
@@ -2446,10 +2446,10 @@
         <v>0.7331868387061853</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2775608295367391</v>
+        <v>0.2775608295367392</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4556260091694462</v>
+        <v>0.4556260091694461</v>
       </c>
     </row>
     <row r="122">
@@ -2478,10 +2478,10 @@
         <v>0.7286654103748402</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3728797892852014</v>
+        <v>0.3728797892852013</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3557856210896388</v>
+        <v>0.355785621089639</v>
       </c>
     </row>
     <row r="124">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5156610875610959</v>
+        <v>0.5156610875610957</v>
       </c>
       <c r="C124" t="n">
-        <v>0.4113353928138187</v>
+        <v>0.4113353928138188</v>
       </c>
       <c r="D124" t="n">
-        <v>0.1043256947472772</v>
+        <v>0.104325694747277</v>
       </c>
     </row>
     <row r="125">
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.2810848197779969</v>
+        <v>0.281084819777997</v>
       </c>
       <c r="C125" t="n">
-        <v>0.5589770737654576</v>
+        <v>0.5589770737654575</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.2778922539874607</v>
+        <v>-0.2778922539874605</v>
       </c>
     </row>
     <row r="126">
@@ -2526,10 +2526,10 @@
         <v>0.2906595706694708</v>
       </c>
       <c r="C126" t="n">
-        <v>0.554996379103301</v>
+        <v>0.5549963791033009</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.2643368084338302</v>
+        <v>-0.2643368084338301</v>
       </c>
     </row>
     <row r="127">
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3503657345749583</v>
+        <v>0.3503657345749582</v>
       </c>
       <c r="C127" t="n">
         <v>0.54800361784109</v>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6401740998721446</v>
+        <v>0.6401740998721447</v>
       </c>
       <c r="C131" t="n">
         <v>0.4853575215344046</v>
       </c>
       <c r="D131" t="n">
-        <v>0.1548165783377399</v>
+        <v>0.15481657833774</v>
       </c>
     </row>
     <row r="132">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.2495821454653234</v>
+        <v>0.2495821454653235</v>
       </c>
       <c r="C132" t="n">
         <v>0.5333703062025809</v>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.3326224677185819</v>
+        <v>0.3326224677185818</v>
       </c>
       <c r="C133" t="n">
         <v>0.6215009457109943</v>
@@ -2686,10 +2686,10 @@
         <v>0.2730153928487399</v>
       </c>
       <c r="C136" t="n">
-        <v>0.5101492053888722</v>
+        <v>0.510149205388872</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.2371338125401323</v>
+        <v>-0.237133812540132</v>
       </c>
     </row>
     <row r="137">
@@ -2702,10 +2702,10 @@
         <v>0.2646222896202271</v>
       </c>
       <c r="C137" t="n">
-        <v>0.6486813519236586</v>
+        <v>0.6486813519236587</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.3840590623034315</v>
+        <v>-0.3840590623034316</v>
       </c>
     </row>
     <row r="138">
@@ -2718,10 +2718,10 @@
         <v>0.3263348973686405</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4071858757528258</v>
+        <v>0.4071858757528256</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.08085097838418537</v>
+        <v>-0.08085097838418515</v>
       </c>
     </row>
     <row r="139">
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4394157850143329</v>
+        <v>0.439415785014333</v>
       </c>
       <c r="C140" t="n">
         <v>0.4099397433899539</v>
       </c>
       <c r="D140" t="n">
-        <v>0.029476041624379</v>
+        <v>0.02947604162437911</v>
       </c>
     </row>
     <row r="141">
@@ -2766,10 +2766,10 @@
         <v>0.3536585898189726</v>
       </c>
       <c r="C141" t="n">
-        <v>0.5241752147329245</v>
+        <v>0.5241752147329244</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.1705166249139519</v>
+        <v>-0.1705166249139518</v>
       </c>
     </row>
     <row r="142">
@@ -2782,10 +2782,10 @@
         <v>0.2585595247916839</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4555523471660755</v>
+        <v>0.4555523471660753</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.1969928223743916</v>
+        <v>-0.1969928223743915</v>
       </c>
     </row>
     <row r="143">
@@ -2798,10 +2798,10 @@
         <v>0.3121234780338815</v>
       </c>
       <c r="C143" t="n">
-        <v>0.5552202024646543</v>
+        <v>0.5552202024646542</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.2430967244307728</v>
+        <v>-0.2430967244307727</v>
       </c>
     </row>
     <row r="144">
@@ -2814,10 +2814,10 @@
         <v>0.2422277310487854</v>
       </c>
       <c r="C144" t="n">
-        <v>0.5846044666892781</v>
+        <v>0.5846044666892782</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.3423767356404927</v>
+        <v>-0.3423767356404928</v>
       </c>
     </row>
     <row r="145">
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.3376177337071652</v>
+        <v>0.3376177337071653</v>
       </c>
       <c r="C146" t="n">
         <v>0.536930090721032</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.1993123570138668</v>
+        <v>-0.1993123570138667</v>
       </c>
     </row>
     <row r="147">
@@ -2862,10 +2862,10 @@
         <v>0.4098737204091548</v>
       </c>
       <c r="C147" t="n">
-        <v>0.564211332031644</v>
+        <v>0.5642113320316439</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.1543376116224892</v>
+        <v>-0.1543376116224891</v>
       </c>
     </row>
     <row r="148">
@@ -2894,10 +2894,10 @@
         <v>0.3421190823220358</v>
       </c>
       <c r="C149" t="n">
-        <v>0.6288214210415348</v>
+        <v>0.628821421041535</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.286702338719499</v>
+        <v>-0.2867023387194992</v>
       </c>
     </row>
     <row r="150">
@@ -2926,10 +2926,10 @@
         <v>0.1959804336258424</v>
       </c>
       <c r="C151" t="n">
-        <v>0.5528528693696585</v>
+        <v>0.5528528693696584</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.3568724357438161</v>
+        <v>-0.356872435743816</v>
       </c>
     </row>
     <row r="152">
@@ -2939,13 +2939,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.2582271181809174</v>
+        <v>0.2582271181809173</v>
       </c>
       <c r="C152" t="n">
         <v>0.5220943449843706</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.2638672268034532</v>
+        <v>-0.2638672268034533</v>
       </c>
     </row>
     <row r="153">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.3083554755859022</v>
+        <v>0.3083554755859021</v>
       </c>
       <c r="C154" t="n">
         <v>0.4662867016839461</v>
@@ -3022,10 +3022,10 @@
         <v>0.2948062503792229</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6016135143476122</v>
+        <v>0.6016135143476121</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.3068072639683894</v>
+        <v>-0.3068072639683892</v>
       </c>
     </row>
     <row r="158">
@@ -3041,7 +3041,7 @@
         <v>0.3459995966596082</v>
       </c>
       <c r="D158" t="n">
-        <v>0.388409922173638</v>
+        <v>0.3884099221736381</v>
       </c>
     </row>
     <row r="159">
@@ -3070,10 +3070,10 @@
         <v>0.2029077175517238</v>
       </c>
       <c r="C160" t="n">
-        <v>0.4514761647217714</v>
+        <v>0.4514761647217715</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.2485684471700476</v>
+        <v>-0.2485684471700477</v>
       </c>
     </row>
     <row r="161">
@@ -3086,10 +3086,10 @@
         <v>0.3636654911302218</v>
       </c>
       <c r="C161" t="n">
-        <v>0.5402973718706745</v>
+        <v>0.5402973718706744</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.1766318807404527</v>
+        <v>-0.1766318807404526</v>
       </c>
     </row>
     <row r="162">
@@ -3102,10 +3102,10 @@
         <v>0.298102161232266</v>
       </c>
       <c r="C162" t="n">
-        <v>0.5374892671732866</v>
+        <v>0.5374892671732867</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.2393871059410206</v>
+        <v>-0.2393871059410207</v>
       </c>
     </row>
     <row r="163">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.3713804674121479</v>
+        <v>0.371380467412148</v>
       </c>
       <c r="C164" t="n">
         <v>0.5506948454931294</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.1793143780809815</v>
+        <v>-0.1793143780809814</v>
       </c>
     </row>
     <row r="165">
@@ -3163,13 +3163,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.4330893647781693</v>
+        <v>0.4330893647781694</v>
       </c>
       <c r="C166" t="n">
-        <v>0.5378819129334764</v>
+        <v>0.5378819129334763</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.1047925481553071</v>
+        <v>-0.1047925481553069</v>
       </c>
     </row>
     <row r="167">
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.5450189425934002</v>
+        <v>0.5450189425934001</v>
       </c>
       <c r="C168" t="n">
         <v>0.4900906599198819</v>
       </c>
       <c r="D168" t="n">
-        <v>0.05492828267351829</v>
+        <v>0.05492828267351818</v>
       </c>
     </row>
     <row r="169">
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.223313074645473</v>
+        <v>0.2233130746454729</v>
       </c>
       <c r="C169" t="n">
-        <v>0.4582932284648316</v>
+        <v>0.4582932284648315</v>
       </c>
       <c r="D169" t="n">
         <v>-0.2349801538193586</v>
@@ -3233,7 +3233,7 @@
         <v>0.472413961688774</v>
       </c>
       <c r="D170" t="n">
-        <v>0.0621866636634395</v>
+        <v>0.06218666366343956</v>
       </c>
     </row>
     <row r="171">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.3756674868794331</v>
+        <v>0.375667486879433</v>
       </c>
       <c r="C171" t="n">
         <v>0.4824760822203277</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.1068085953408946</v>
+        <v>-0.1068085953408947</v>
       </c>
     </row>
     <row r="172">
@@ -3278,10 +3278,10 @@
         <v>0.3731151803093062</v>
       </c>
       <c r="C173" t="n">
-        <v>0.4728745947498526</v>
+        <v>0.4728745947498525</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.09975941444054637</v>
+        <v>-0.09975941444054631</v>
       </c>
     </row>
     <row r="174">
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.3927444127097622</v>
+        <v>0.3927444127097621</v>
       </c>
       <c r="C174" t="n">
         <v>0.5742597023225684</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.1815152896128062</v>
+        <v>-0.1815152896128063</v>
       </c>
     </row>
     <row r="175">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.3461594704891463</v>
+        <v>0.3461594704891462</v>
       </c>
       <c r="C175" t="n">
-        <v>0.3706125273858959</v>
+        <v>0.370612527385896</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.02445305689674959</v>
+        <v>-0.02445305689674976</v>
       </c>
     </row>
     <row r="176">
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.3020002453217534</v>
+        <v>0.3020002453217535</v>
       </c>
       <c r="C177" t="n">
-        <v>0.5702981052168413</v>
+        <v>0.5702981052168412</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.2682978598950879</v>
+        <v>-0.2682978598950878</v>
       </c>
     </row>
     <row r="178">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.6952676036910012</v>
+        <v>0.695267603691001</v>
       </c>
       <c r="C178" t="n">
         <v>0.3129134620966978</v>
@@ -3374,7 +3374,7 @@
         <v>0.3060753364771185</v>
       </c>
       <c r="C179" t="n">
-        <v>0.4875827688095652</v>
+        <v>0.4875827688095653</v>
       </c>
       <c r="D179" t="n">
         <v>-0.1815074323324468</v>
@@ -3422,10 +3422,10 @@
         <v>0.4112568200102232</v>
       </c>
       <c r="C182" t="n">
-        <v>0.4634854721068729</v>
+        <v>0.463485472106873</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.05222865209664967</v>
+        <v>-0.05222865209664979</v>
       </c>
     </row>
     <row r="183">
@@ -3438,10 +3438,10 @@
         <v>0.4887167271458996</v>
       </c>
       <c r="C183" t="n">
-        <v>0.4138600897737933</v>
+        <v>0.4138600897737932</v>
       </c>
       <c r="D183" t="n">
-        <v>0.07485663737210629</v>
+        <v>0.0748566373721064</v>
       </c>
     </row>
     <row r="184">
@@ -3483,13 +3483,13 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.691173087592525</v>
+        <v>0.6911730875925248</v>
       </c>
       <c r="C186" t="n">
         <v>0.4359135659874048</v>
       </c>
       <c r="D186" t="n">
-        <v>0.2552595216051203</v>
+        <v>0.2552595216051201</v>
       </c>
     </row>
     <row r="187">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.5117210979763573</v>
+        <v>0.5117210979763575</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3317711532174035</v>
+        <v>0.3317711532174036</v>
       </c>
       <c r="D188" t="n">
-        <v>0.1799499447589538</v>
+        <v>0.1799499447589539</v>
       </c>
     </row>
     <row r="189">
@@ -3534,10 +3534,10 @@
         <v>0.2425863285940837</v>
       </c>
       <c r="C189" t="n">
-        <v>0.4789040752657616</v>
+        <v>0.4789040752657617</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.2363177466716778</v>
+        <v>-0.236317746671678</v>
       </c>
     </row>
     <row r="190">
@@ -3550,10 +3550,10 @@
         <v>0.2676401400516573</v>
       </c>
       <c r="C190" t="n">
-        <v>0.4497982534138792</v>
+        <v>0.449798253413879</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.182158113362222</v>
+        <v>-0.1821581133622218</v>
       </c>
     </row>
     <row r="191">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2457170183017886</v>
+        <v>0.2457170183017885</v>
       </c>
       <c r="C193" t="n">
         <v>0.5387749146721179</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2930578963703293</v>
+        <v>-0.2930578963703294</v>
       </c>
     </row>
     <row r="194">
@@ -3614,10 +3614,10 @@
         <v>0.3384152476636595</v>
       </c>
       <c r="C194" t="n">
-        <v>0.6939670055337078</v>
+        <v>0.6939670055337079</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.3555517578700483</v>
+        <v>-0.3555517578700484</v>
       </c>
     </row>
     <row r="195">
@@ -3630,7 +3630,7 @@
         <v>0.6307558398144983</v>
       </c>
       <c r="C195" t="n">
-        <v>0.3688662468259861</v>
+        <v>0.368866246825986</v>
       </c>
       <c r="D195" t="n">
         <v>0.2618895929885123</v>
@@ -3678,10 +3678,10 @@
         <v>0.2048307869197235</v>
       </c>
       <c r="C198" t="n">
-        <v>0.5874167728490803</v>
+        <v>0.5874167728490804</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.3825859859293569</v>
+        <v>-0.382585985929357</v>
       </c>
     </row>
     <row r="199">
@@ -3691,13 +3691,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.4725839845054431</v>
+        <v>0.4725839845054432</v>
       </c>
       <c r="C199" t="n">
-        <v>0.4719938154473259</v>
+        <v>0.4719938154473258</v>
       </c>
       <c r="D199" t="n">
-        <v>0.000590169058117207</v>
+        <v>0.0005901690581173735</v>
       </c>
     </row>
     <row r="200">
@@ -3707,13 +3707,13 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.3353199157175726</v>
+        <v>0.3353199157175727</v>
       </c>
       <c r="C200" t="n">
         <v>0.3679258831473995</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.03260596742982691</v>
+        <v>-0.03260596742982685</v>
       </c>
     </row>
     <row r="201">
@@ -3726,10 +3726,10 @@
         <v>0.2681894949034624</v>
       </c>
       <c r="C201" t="n">
-        <v>0.5037247874060019</v>
+        <v>0.5037247874060018</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.2355352925025395</v>
+        <v>-0.2355352925025394</v>
       </c>
     </row>
     <row r="202">
@@ -3758,10 +3758,10 @@
         <v>0.2845583924702809</v>
       </c>
       <c r="C203" t="n">
-        <v>0.4889509177521717</v>
+        <v>0.4889509177521718</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.2043925252818908</v>
+        <v>-0.2043925252818909</v>
       </c>
     </row>
     <row r="204">
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.2807292778417274</v>
+        <v>0.2807292778417272</v>
       </c>
       <c r="C204" t="n">
-        <v>0.4631967170536596</v>
+        <v>0.4631967170536595</v>
       </c>
       <c r="D204" t="n">
         <v>-0.1824674392119323</v>
@@ -3806,10 +3806,10 @@
         <v>0.6630496986078209</v>
       </c>
       <c r="C206" t="n">
-        <v>0.3522360946872125</v>
+        <v>0.3522360946872126</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3108136039206084</v>
+        <v>0.3108136039206083</v>
       </c>
     </row>
     <row r="207">

--- a/results/GSE186332/glass_recurrence_score_gse186332_universe.xlsx
+++ b/results/GSE186332/glass_recurrence_score_gse186332_universe.xlsx
@@ -539,10 +539,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3517171867968006</v>
+        <v>0.3517171867968008</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6145295737119844</v>
+        <v>0.6145295737119845</v>
       </c>
       <c r="D2" t="n">
         <v>-0.2628123869151837</v>
@@ -574,10 +574,10 @@
         <v>0.321586044422444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5835212532885992</v>
+        <v>0.5835212532885993</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2619352088661551</v>
+        <v>-0.2619352088661552</v>
       </c>
     </row>
     <row r="5">
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4381573106100786</v>
+        <v>0.4381573106100785</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4439456162705069</v>
+        <v>0.443945616270507</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.005788305660428372</v>
+        <v>-0.005788305660428594</v>
       </c>
     </row>
     <row r="8">
@@ -638,10 +638,10 @@
         <v>0.3242957148575497</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4978030171083549</v>
+        <v>0.497803017108355</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1735073022508052</v>
+        <v>-0.1735073022508054</v>
       </c>
     </row>
     <row r="9">
@@ -654,10 +654,10 @@
         <v>0.7541570469546709</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2933250984670009</v>
+        <v>0.293325098467001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.46083194848767</v>
+        <v>0.4608319484876699</v>
       </c>
     </row>
     <row r="10">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.424864974819599</v>
+        <v>0.4248649748195991</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6310428488054097</v>
+        <v>0.6310428488054096</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2061778739858107</v>
+        <v>-0.2061778739858106</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +689,7 @@
         <v>0.3674919866653222</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2550180739274049</v>
+        <v>0.2550180739274048</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>0.5388322073414062</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2249146502920945</v>
+        <v>-0.2249146502920944</v>
       </c>
     </row>
     <row r="13">
@@ -718,10 +718,10 @@
         <v>0.2518140496030109</v>
       </c>
       <c r="C13" t="n">
-        <v>0.52616899962416</v>
+        <v>0.5261689996241601</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2743549500211491</v>
+        <v>-0.2743549500211492</v>
       </c>
     </row>
     <row r="14">
@@ -734,10 +734,10 @@
         <v>0.2761733647799154</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6049059330760511</v>
+        <v>0.604905933076051</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3287325682961357</v>
+        <v>-0.3287325682961356</v>
       </c>
     </row>
     <row r="15">
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4155030252711962</v>
+        <v>0.4155030252711961</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5398168773509091</v>
+        <v>0.5398168773509093</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1243138520797129</v>
+        <v>-0.1243138520797132</v>
       </c>
     </row>
     <row r="17">
@@ -801,7 +801,7 @@
         <v>0.4694484931264075</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1039426523297491</v>
+        <v>0.1039426523297492</v>
       </c>
     </row>
     <row r="19">
@@ -830,10 +830,10 @@
         <v>0.5691320629857054</v>
       </c>
       <c r="C20" t="n">
-        <v>0.448071834312656</v>
+        <v>0.4480718343126561</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1210602286730494</v>
+        <v>0.1210602286730493</v>
       </c>
     </row>
     <row r="21">
@@ -846,10 +846,10 @@
         <v>0.4228836306222661</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4587378195785093</v>
+        <v>0.4587378195785092</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0358541889562432</v>
+        <v>-0.03585418895624309</v>
       </c>
     </row>
     <row r="22">
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.589701549935854</v>
+        <v>0.5897015499358541</v>
       </c>
       <c r="C22" t="n">
         <v>0.3666261034568105</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2230754464790435</v>
+        <v>0.2230754464790436</v>
       </c>
     </row>
     <row r="23">
@@ -878,10 +878,10 @@
         <v>0.3299320039687996</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5763291135372646</v>
+        <v>0.5763291135372647</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2463971095684649</v>
+        <v>-0.2463971095684651</v>
       </c>
     </row>
     <row r="24">
@@ -942,10 +942,10 @@
         <v>0.2333891636754437</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5752161079485557</v>
+        <v>0.5752161079485558</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.341826944273112</v>
+        <v>-0.3418269442731121</v>
       </c>
     </row>
     <row r="28">
@@ -990,10 +990,10 @@
         <v>0.21300475932932</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5413714184442673</v>
+        <v>0.5413714184442672</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3283666591149473</v>
+        <v>-0.3283666591149472</v>
       </c>
     </row>
     <row r="31">
@@ -1073,7 +1073,7 @@
         <v>0.3756771993509886</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3169304966805174</v>
+        <v>0.3169304966805173</v>
       </c>
     </row>
     <row r="36">
@@ -1086,10 +1086,10 @@
         <v>0.2133341103310578</v>
       </c>
       <c r="C36" t="n">
-        <v>0.540638072277376</v>
+        <v>0.5406380722773759</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3273039619463183</v>
+        <v>-0.3273039619463182</v>
       </c>
     </row>
     <row r="37">
@@ -1102,10 +1102,10 @@
         <v>0.2299166822720985</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4833354722596533</v>
+        <v>0.4833354722596536</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2534187899875548</v>
+        <v>-0.2534187899875551</v>
       </c>
     </row>
     <row r="38">
@@ -1118,10 +1118,10 @@
         <v>0.5802619006150068</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4882343774349384</v>
+        <v>0.4882343774349385</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09202752318006846</v>
+        <v>0.09202752318006829</v>
       </c>
     </row>
     <row r="39">
@@ -1166,10 +1166,10 @@
         <v>0.3049331934737429</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5667864465405922</v>
+        <v>0.5667864465405923</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2618532530668493</v>
+        <v>-0.2618532530668494</v>
       </c>
     </row>
     <row r="42">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5195967119900788</v>
+        <v>0.519596711990079</v>
       </c>
       <c r="C44" t="n">
-        <v>0.317520174658612</v>
+        <v>0.3175201746586121</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2020765373314668</v>
+        <v>0.2020765373314669</v>
       </c>
     </row>
     <row r="45">
@@ -1230,10 +1230,10 @@
         <v>0.2778196832730287</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4899264209345887</v>
+        <v>0.4899264209345886</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.21210673766156</v>
+        <v>-0.2121067376615599</v>
       </c>
     </row>
     <row r="46">
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2610238734733414</v>
+        <v>0.2610238734733413</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5738410838856346</v>
+        <v>0.5738410838856347</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3128172104122932</v>
+        <v>-0.3128172104122934</v>
       </c>
     </row>
     <row r="47">
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4909150195842714</v>
+        <v>0.4909150195842713</v>
       </c>
       <c r="C47" t="n">
-        <v>0.615046735540094</v>
+        <v>0.6150467355400941</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1241317159558227</v>
+        <v>-0.1241317159558229</v>
       </c>
     </row>
     <row r="48">
@@ -1278,10 +1278,10 @@
         <v>0.2549028338154648</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5939790751893714</v>
+        <v>0.5939790751893713</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3390762413739066</v>
+        <v>-0.3390762413739065</v>
       </c>
     </row>
     <row r="49">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6302289655148331</v>
+        <v>0.630228965514833</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3412863197328176</v>
+        <v>0.3412863197328175</v>
       </c>
       <c r="D49" t="n">
         <v>0.2889426457820155</v>
@@ -1310,10 +1310,10 @@
         <v>0.5916228732415516</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3721601933589394</v>
+        <v>0.3721601933589393</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2194626798826122</v>
+        <v>0.2194626798826123</v>
       </c>
     </row>
     <row r="51">
@@ -1326,10 +1326,10 @@
         <v>0.4523353365033095</v>
       </c>
       <c r="C51" t="n">
-        <v>0.465768012051322</v>
+        <v>0.4657680120513221</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.01343267554801253</v>
+        <v>-0.01343267554801264</v>
       </c>
     </row>
     <row r="52">
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3449088533652514</v>
+        <v>0.3449088533652513</v>
       </c>
       <c r="C52" t="n">
         <v>0.602559225341999</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2576503719767476</v>
+        <v>-0.2576503719767477</v>
       </c>
     </row>
     <row r="53">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5184910180372602</v>
+        <v>0.5184910180372601</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5152268636923369</v>
+        <v>0.5152268636923368</v>
       </c>
       <c r="D53" t="n">
         <v>0.00326415434492322</v>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.576815173630618</v>
+        <v>0.5768151736306179</v>
       </c>
       <c r="C55" t="n">
         <v>0.3471565266281049</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2296586470025131</v>
+        <v>0.2296586470025129</v>
       </c>
     </row>
     <row r="56">
@@ -1406,10 +1406,10 @@
         <v>0.2557191179417068</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5067215759609126</v>
+        <v>0.5067215759609127</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.2510024580192058</v>
+        <v>-0.2510024580192059</v>
       </c>
     </row>
     <row r="57">
@@ -1454,10 +1454,10 @@
         <v>0.2383161149764566</v>
       </c>
       <c r="C59" t="n">
-        <v>0.6466256909495918</v>
+        <v>0.6466256909495917</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4083095759731352</v>
+        <v>-0.4083095759731351</v>
       </c>
     </row>
     <row r="60">
@@ -1489,7 +1489,7 @@
         <v>0.4959123590218384</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.2768457078951263</v>
+        <v>-0.2768457078951262</v>
       </c>
     </row>
     <row r="62">
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5571169717692283</v>
+        <v>0.5571169717692281</v>
       </c>
       <c r="C64" t="n">
         <v>0.5156836772421295</v>
       </c>
       <c r="D64" t="n">
-        <v>0.04143329452709876</v>
+        <v>0.04143329452709865</v>
       </c>
     </row>
     <row r="65">
@@ -1550,10 +1550,10 @@
         <v>0.4236920574681486</v>
       </c>
       <c r="C65" t="n">
-        <v>0.424709793532498</v>
+        <v>0.4247097935324979</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.001017736064349462</v>
+        <v>-0.00101773606434935</v>
       </c>
     </row>
     <row r="66">
@@ -1566,10 +1566,10 @@
         <v>0.2531877641192054</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6337084857318336</v>
+        <v>0.6337084857318337</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.3805207216126282</v>
+        <v>-0.3805207216126283</v>
       </c>
     </row>
     <row r="67">
@@ -1582,10 +1582,10 @@
         <v>0.2324478178368121</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5449778010004065</v>
+        <v>0.5449778010004064</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.3125299831635944</v>
+        <v>-0.3125299831635943</v>
       </c>
     </row>
     <row r="68">
@@ -1598,10 +1598,10 @@
         <v>0.215393372558623</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4741785759028559</v>
+        <v>0.4741785759028561</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.258785203344233</v>
+        <v>-0.2587852033442331</v>
       </c>
     </row>
     <row r="69">
@@ -1614,10 +1614,10 @@
         <v>0.3953477916022261</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4541284333586948</v>
+        <v>0.4541284333586949</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.0587806417564688</v>
+        <v>-0.05878064175646885</v>
       </c>
     </row>
     <row r="70">
@@ -1646,10 +1646,10 @@
         <v>0.367556372712713</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5785887364139983</v>
+        <v>0.5785887364139984</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.2110323637012854</v>
+        <v>-0.2110323637012855</v>
       </c>
     </row>
     <row r="72">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.2633352234457754</v>
+        <v>0.2633352234457753</v>
       </c>
       <c r="C72" t="n">
         <v>0.4891495323390382</v>
@@ -1681,7 +1681,7 @@
         <v>0.4560916621596434</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.1246842355455506</v>
+        <v>-0.1246842355455507</v>
       </c>
     </row>
     <row r="74">
@@ -1694,10 +1694,10 @@
         <v>0.4612053329980894</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4954570732765602</v>
+        <v>0.4954570732765601</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.03425174027847083</v>
+        <v>-0.03425174027847078</v>
       </c>
     </row>
     <row r="75">
@@ -1761,7 +1761,7 @@
         <v>0.3860021022590118</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.04938748134441562</v>
+        <v>-0.04938748134441556</v>
       </c>
     </row>
     <row r="79">
@@ -1806,10 +1806,10 @@
         <v>0.249440277903276</v>
       </c>
       <c r="C81" t="n">
-        <v>0.377438757956042</v>
+        <v>0.3774387579560421</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.127998480052766</v>
+        <v>-0.1279984800527662</v>
       </c>
     </row>
     <row r="82">
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5674139376804173</v>
+        <v>0.5674139376804174</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3701083518961581</v>
+        <v>0.3701083518961582</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1973055857842591</v>
+        <v>0.1973055857842592</v>
       </c>
     </row>
     <row r="85">
@@ -1873,7 +1873,7 @@
         <v>0.4252613309621807</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.1924795787100877</v>
+        <v>-0.1924795787100878</v>
       </c>
     </row>
     <row r="86">
@@ -1899,13 +1899,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5148731769472632</v>
+        <v>0.5148731769472633</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5051700904765833</v>
+        <v>0.5051700904765832</v>
       </c>
       <c r="D87" t="n">
-        <v>0.009703086470679856</v>
+        <v>0.009703086470680078</v>
       </c>
     </row>
     <row r="88">
@@ -1934,10 +1934,10 @@
         <v>0.224397161077303</v>
       </c>
       <c r="C89" t="n">
-        <v>0.527891981165226</v>
+        <v>0.5278919811652258</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.3034948200879229</v>
+        <v>-0.3034948200879228</v>
       </c>
     </row>
     <row r="90">
@@ -1966,10 +1966,10 @@
         <v>0.7205379268740377</v>
       </c>
       <c r="C91" t="n">
-        <v>0.40113920743613</v>
+        <v>0.4011392074361301</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3193987194379077</v>
+        <v>0.3193987194379076</v>
       </c>
     </row>
     <row r="92">
@@ -1982,10 +1982,10 @@
         <v>0.2299406906287527</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6353023677914363</v>
+        <v>0.6353023677914365</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.4053616771626837</v>
+        <v>-0.4053616771626838</v>
       </c>
     </row>
     <row r="93">
@@ -2014,10 +2014,10 @@
         <v>0.2000339172602187</v>
       </c>
       <c r="C94" t="n">
-        <v>0.5942380380545549</v>
+        <v>0.5942380380545548</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.3942041207943362</v>
+        <v>-0.3942041207943361</v>
       </c>
     </row>
     <row r="95">
@@ -2030,10 +2030,10 @@
         <v>0.6026551496397219</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3374477108904961</v>
+        <v>0.3374477108904962</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2652074387492258</v>
+        <v>0.2652074387492257</v>
       </c>
     </row>
     <row r="96">
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.487090270111473</v>
+        <v>0.4870902701114729</v>
       </c>
       <c r="C97" t="n">
         <v>0.3997821350762527</v>
       </c>
       <c r="D97" t="n">
-        <v>0.08730813503522034</v>
+        <v>0.08730813503522022</v>
       </c>
     </row>
     <row r="98">
@@ -2078,10 +2078,10 @@
         <v>0.5028030847682692</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4328675057369059</v>
+        <v>0.432867505736906</v>
       </c>
       <c r="D98" t="n">
-        <v>0.06993557903136327</v>
+        <v>0.06993557903136316</v>
       </c>
     </row>
     <row r="99">
@@ -2110,10 +2110,10 @@
         <v>0.395217709960718</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6453499741801035</v>
+        <v>0.6453499741801038</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.2501322642193855</v>
+        <v>-0.2501322642193858</v>
       </c>
     </row>
     <row r="101">
@@ -2142,10 +2142,10 @@
         <v>0.2694488423388679</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6047363467749575</v>
+        <v>0.6047363467749576</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.3352875044360896</v>
+        <v>-0.3352875044360897</v>
       </c>
     </row>
     <row r="103">
@@ -2158,10 +2158,10 @@
         <v>0.4061419487539445</v>
       </c>
       <c r="C103" t="n">
-        <v>0.4919584009386831</v>
+        <v>0.491958400938683</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.08581645218473866</v>
+        <v>-0.08581645218473855</v>
       </c>
     </row>
     <row r="104">
@@ -2190,10 +2190,10 @@
         <v>0.5644639654209821</v>
       </c>
       <c r="C105" t="n">
-        <v>0.5441772314348834</v>
+        <v>0.5441772314348835</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0202867339860987</v>
+        <v>0.02028673398609859</v>
       </c>
     </row>
     <row r="106">
@@ -2257,7 +2257,7 @@
         <v>0.3697737627075141</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3393601947557892</v>
+        <v>0.3393601947557891</v>
       </c>
     </row>
     <row r="110">
@@ -2270,10 +2270,10 @@
         <v>0.3618456576958351</v>
       </c>
       <c r="C110" t="n">
-        <v>0.5331441911344559</v>
+        <v>0.533144191134456</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.1712985334386208</v>
+        <v>-0.1712985334386209</v>
       </c>
     </row>
     <row r="111">
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.3660665450534273</v>
+        <v>0.3660665450534274</v>
       </c>
       <c r="C111" t="n">
         <v>0.5419275392874932</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4670114266682206</v>
+        <v>0.4670114266682207</v>
       </c>
       <c r="C113" t="n">
         <v>0.5966145379766369</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.1296031113084163</v>
+        <v>-0.1296031113084162</v>
       </c>
     </row>
     <row r="114">
@@ -2334,10 +2334,10 @@
         <v>0.503966398777058</v>
       </c>
       <c r="C114" t="n">
-        <v>0.5250575218399655</v>
+        <v>0.5250575218399656</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.0210911230629075</v>
+        <v>-0.02109112306290761</v>
       </c>
     </row>
     <row r="115">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5158725793574404</v>
+        <v>0.5158725793574402</v>
       </c>
       <c r="C115" t="n">
         <v>0.4944678198535141</v>
       </c>
       <c r="D115" t="n">
-        <v>0.02140475950392623</v>
+        <v>0.02140475950392612</v>
       </c>
     </row>
     <row r="116">
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6548157053065889</v>
+        <v>0.6548157053065888</v>
       </c>
       <c r="C119" t="n">
-        <v>0.3615755636834755</v>
+        <v>0.3615755636834756</v>
       </c>
       <c r="D119" t="n">
-        <v>0.2932401416231134</v>
+        <v>0.2932401416231132</v>
       </c>
     </row>
     <row r="120">
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5389596698894611</v>
+        <v>0.5389596698894612</v>
       </c>
       <c r="C120" t="n">
-        <v>0.5530873873626121</v>
+        <v>0.5530873873626122</v>
       </c>
       <c r="D120" t="n">
         <v>-0.014127717473151</v>
@@ -2446,10 +2446,10 @@
         <v>0.7331868387061853</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2775608295367392</v>
+        <v>0.2775608295367391</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4556260091694461</v>
+        <v>0.4556260091694462</v>
       </c>
     </row>
     <row r="122">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.6519285912900302</v>
+        <v>0.6519285912900301</v>
       </c>
       <c r="C122" t="n">
-        <v>0.4405122575756186</v>
+        <v>0.4405122575756188</v>
       </c>
       <c r="D122" t="n">
-        <v>0.2114163337144117</v>
+        <v>0.2114163337144113</v>
       </c>
     </row>
     <row r="123">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.7286654103748402</v>
+        <v>0.7286654103748403</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3728797892852013</v>
+        <v>0.3728797892852014</v>
       </c>
       <c r="D123" t="n">
-        <v>0.355785621089639</v>
+        <v>0.3557856210896389</v>
       </c>
     </row>
     <row r="124">
@@ -2494,7 +2494,7 @@
         <v>0.5156610875610957</v>
       </c>
       <c r="C124" t="n">
-        <v>0.4113353928138188</v>
+        <v>0.4113353928138187</v>
       </c>
       <c r="D124" t="n">
         <v>0.104325694747277</v>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.281084819777997</v>
+        <v>0.2810848197779969</v>
       </c>
       <c r="C125" t="n">
-        <v>0.5589770737654575</v>
+        <v>0.5589770737654576</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.2778922539874605</v>
+        <v>-0.2778922539874606</v>
       </c>
     </row>
     <row r="126">
@@ -2526,10 +2526,10 @@
         <v>0.2906595706694708</v>
       </c>
       <c r="C126" t="n">
-        <v>0.5549963791033009</v>
+        <v>0.554996379103301</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.2643368084338301</v>
+        <v>-0.2643368084338302</v>
       </c>
     </row>
     <row r="127">
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3503657345749582</v>
+        <v>0.3503657345749583</v>
       </c>
       <c r="C127" t="n">
         <v>0.54800361784109</v>
@@ -2558,10 +2558,10 @@
         <v>0.3578467385084001</v>
       </c>
       <c r="C128" t="n">
-        <v>0.616994686295899</v>
+        <v>0.6169946862958992</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.2591479477874989</v>
+        <v>-0.2591479477874991</v>
       </c>
     </row>
     <row r="129">
@@ -2590,10 +2590,10 @@
         <v>0.3982480010860507</v>
       </c>
       <c r="C130" t="n">
-        <v>0.6174430969208629</v>
+        <v>0.6174430969208627</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.2191950958348121</v>
+        <v>-0.219195095834812</v>
       </c>
     </row>
     <row r="131">
@@ -2622,10 +2622,10 @@
         <v>0.2495821454653235</v>
       </c>
       <c r="C132" t="n">
-        <v>0.5333703062025809</v>
+        <v>0.5333703062025807</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.2837881607372574</v>
+        <v>-0.2837881607372573</v>
       </c>
     </row>
     <row r="133">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.3326224677185818</v>
+        <v>0.3326224677185819</v>
       </c>
       <c r="C133" t="n">
         <v>0.6215009457109943</v>
@@ -2670,10 +2670,10 @@
         <v>0.271510068886523</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6528514943455954</v>
+        <v>0.6528514943455955</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.3813414254590725</v>
+        <v>-0.3813414254590726</v>
       </c>
     </row>
     <row r="136">
@@ -2686,10 +2686,10 @@
         <v>0.2730153928487399</v>
       </c>
       <c r="C136" t="n">
-        <v>0.510149205388872</v>
+        <v>0.5101492053888721</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.237133812540132</v>
+        <v>-0.2371338125401322</v>
       </c>
     </row>
     <row r="137">
@@ -2699,13 +2699,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.2646222896202271</v>
+        <v>0.264622289620227</v>
       </c>
       <c r="C137" t="n">
         <v>0.6486813519236587</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.3840590623034316</v>
+        <v>-0.3840590623034317</v>
       </c>
     </row>
     <row r="138">
@@ -2734,10 +2734,10 @@
         <v>0.7277413069014421</v>
       </c>
       <c r="C139" t="n">
-        <v>0.3481675512654805</v>
+        <v>0.3481675512654804</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3795737556359616</v>
+        <v>0.3795737556359617</v>
       </c>
     </row>
     <row r="140">
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.439415785014333</v>
+        <v>0.4394157850143329</v>
       </c>
       <c r="C140" t="n">
         <v>0.4099397433899539</v>
       </c>
       <c r="D140" t="n">
-        <v>0.02947604162437911</v>
+        <v>0.029476041624379</v>
       </c>
     </row>
     <row r="141">
@@ -2766,10 +2766,10 @@
         <v>0.3536585898189726</v>
       </c>
       <c r="C141" t="n">
-        <v>0.5241752147329244</v>
+        <v>0.5241752147329245</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.1705166249139518</v>
+        <v>-0.1705166249139519</v>
       </c>
     </row>
     <row r="142">
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.2585595247916839</v>
+        <v>0.2585595247916838</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4555523471660753</v>
+        <v>0.4555523471660755</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.1969928223743915</v>
+        <v>-0.1969928223743916</v>
       </c>
     </row>
     <row r="143">
@@ -2814,10 +2814,10 @@
         <v>0.2422277310487854</v>
       </c>
       <c r="C144" t="n">
-        <v>0.5846044666892782</v>
+        <v>0.5846044666892781</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.3423767356404928</v>
+        <v>-0.3423767356404927</v>
       </c>
     </row>
     <row r="145">
@@ -2830,10 +2830,10 @@
         <v>0.3662978983084585</v>
       </c>
       <c r="C145" t="n">
-        <v>0.6374878921492236</v>
+        <v>0.6374878921492237</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.2711899938407651</v>
+        <v>-0.2711899938407652</v>
       </c>
     </row>
     <row r="146">
@@ -2894,10 +2894,10 @@
         <v>0.3421190823220358</v>
       </c>
       <c r="C149" t="n">
-        <v>0.628821421041535</v>
+        <v>0.6288214210415348</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.2867023387194992</v>
+        <v>-0.286702338719499</v>
       </c>
     </row>
     <row r="150">
@@ -2939,13 +2939,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.2582271181809173</v>
+        <v>0.2582271181809174</v>
       </c>
       <c r="C152" t="n">
         <v>0.5220943449843706</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.2638672268034533</v>
+        <v>-0.2638672268034532</v>
       </c>
     </row>
     <row r="153">
@@ -2958,10 +2958,10 @@
         <v>0.5586408476434052</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5074602694436041</v>
+        <v>0.5074602694436042</v>
       </c>
       <c r="D153" t="n">
-        <v>0.05118057819980104</v>
+        <v>0.05118057819980093</v>
       </c>
     </row>
     <row r="154">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.3083554755859021</v>
+        <v>0.3083554755859022</v>
       </c>
       <c r="C154" t="n">
         <v>0.4662867016839461</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.157931226098044</v>
+        <v>-0.1579312260980439</v>
       </c>
     </row>
     <row r="155">
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4764240120233851</v>
+        <v>0.476424012023385</v>
       </c>
       <c r="C155" t="n">
         <v>0.45196658997088</v>
       </c>
       <c r="D155" t="n">
-        <v>0.02445742205250506</v>
+        <v>0.02445742205250501</v>
       </c>
     </row>
     <row r="156">
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.2948062503792229</v>
+        <v>0.294806250379223</v>
       </c>
       <c r="C157" t="n">
         <v>0.6016135143476121</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.3068072639683892</v>
+        <v>-0.3068072639683891</v>
       </c>
     </row>
     <row r="158">
@@ -3057,7 +3057,7 @@
         <v>0.4651431400049501</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.1388097704408239</v>
+        <v>-0.138809770440824</v>
       </c>
     </row>
     <row r="160">
@@ -3070,10 +3070,10 @@
         <v>0.2029077175517238</v>
       </c>
       <c r="C160" t="n">
-        <v>0.4514761647217715</v>
+        <v>0.4514761647217714</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.2485684471700477</v>
+        <v>-0.2485684471700476</v>
       </c>
     </row>
     <row r="161">
@@ -3086,10 +3086,10 @@
         <v>0.3636654911302218</v>
       </c>
       <c r="C161" t="n">
-        <v>0.5402973718706744</v>
+        <v>0.5402973718706743</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.1766318807404526</v>
+        <v>-0.1766318807404525</v>
       </c>
     </row>
     <row r="162">
@@ -3102,10 +3102,10 @@
         <v>0.298102161232266</v>
       </c>
       <c r="C162" t="n">
-        <v>0.5374892671732867</v>
+        <v>0.5374892671732866</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.2393871059410207</v>
+        <v>-0.2393871059410206</v>
       </c>
     </row>
     <row r="163">
@@ -3118,10 +3118,10 @@
         <v>0.2608778590133264</v>
       </c>
       <c r="C163" t="n">
-        <v>0.5278113894770936</v>
+        <v>0.5278113894770937</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.2669335304637672</v>
+        <v>-0.2669335304637673</v>
       </c>
     </row>
     <row r="164">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.371380467412148</v>
+        <v>0.3713804674121479</v>
       </c>
       <c r="C164" t="n">
         <v>0.5506948454931294</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.1793143780809814</v>
+        <v>-0.1793143780809815</v>
       </c>
     </row>
     <row r="165">
@@ -3150,10 +3150,10 @@
         <v>0.3344791867191009</v>
       </c>
       <c r="C165" t="n">
-        <v>0.5097748932828546</v>
+        <v>0.5097748932828547</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.1752957065637537</v>
+        <v>-0.1752957065637538</v>
       </c>
     </row>
     <row r="166">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.4330893647781694</v>
+        <v>0.4330893647781693</v>
       </c>
       <c r="C166" t="n">
-        <v>0.5378819129334763</v>
+        <v>0.5378819129334762</v>
       </c>
       <c r="D166" t="n">
         <v>-0.1047925481553069</v>
@@ -3182,10 +3182,10 @@
         <v>0.3123369341503159</v>
       </c>
       <c r="C167" t="n">
-        <v>0.5097260035383951</v>
+        <v>0.5097260035383953</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.1973890693880793</v>
+        <v>-0.1973890693880794</v>
       </c>
     </row>
     <row r="168">
@@ -3201,7 +3201,7 @@
         <v>0.4900906599198819</v>
       </c>
       <c r="D168" t="n">
-        <v>0.05492828267351818</v>
+        <v>0.05492828267351824</v>
       </c>
     </row>
     <row r="169">
@@ -3214,10 +3214,10 @@
         <v>0.2233130746454729</v>
       </c>
       <c r="C169" t="n">
-        <v>0.4582932284648315</v>
+        <v>0.4582932284648314</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.2349801538193586</v>
+        <v>-0.2349801538193585</v>
       </c>
     </row>
     <row r="170">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.375667486879433</v>
+        <v>0.3756674868794331</v>
       </c>
       <c r="C171" t="n">
-        <v>0.4824760822203277</v>
+        <v>0.4824760822203279</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.1068085953408947</v>
+        <v>-0.1068085953408948</v>
       </c>
     </row>
     <row r="172">
@@ -3262,7 +3262,7 @@
         <v>0.4987777563885146</v>
       </c>
       <c r="C172" t="n">
-        <v>0.316639777307214</v>
+        <v>0.3166397773072139</v>
       </c>
       <c r="D172" t="n">
         <v>0.1821379790813006</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.3731151803093062</v>
+        <v>0.3731151803093061</v>
       </c>
       <c r="C173" t="n">
-        <v>0.4728745947498525</v>
+        <v>0.4728745947498527</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.09975941444054631</v>
+        <v>-0.09975941444054653</v>
       </c>
     </row>
     <row r="174">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.3461594704891462</v>
+        <v>0.3461594704891463</v>
       </c>
       <c r="C175" t="n">
-        <v>0.370612527385896</v>
+        <v>0.3706125273858959</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.02445305689674976</v>
+        <v>-0.02445305689674959</v>
       </c>
     </row>
     <row r="176">
@@ -3326,10 +3326,10 @@
         <v>0.2082480491027641</v>
       </c>
       <c r="C176" t="n">
-        <v>0.5553011761039152</v>
+        <v>0.5553011761039153</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.3470531270011511</v>
+        <v>-0.3470531270011512</v>
       </c>
     </row>
     <row r="177">
@@ -3342,10 +3342,10 @@
         <v>0.3020002453217535</v>
       </c>
       <c r="C177" t="n">
-        <v>0.5702981052168412</v>
+        <v>0.5702981052168413</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.2682978598950878</v>
+        <v>-0.2682978598950879</v>
       </c>
     </row>
     <row r="178">
@@ -3355,13 +3355,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.695267603691001</v>
+        <v>0.6952676036910012</v>
       </c>
       <c r="C178" t="n">
         <v>0.3129134620966978</v>
       </c>
       <c r="D178" t="n">
-        <v>0.3823541415943033</v>
+        <v>0.3823541415943034</v>
       </c>
     </row>
     <row r="179">
@@ -3422,10 +3422,10 @@
         <v>0.4112568200102232</v>
       </c>
       <c r="C182" t="n">
-        <v>0.463485472106873</v>
+        <v>0.4634854721068729</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.05222865209664979</v>
+        <v>-0.05222865209664967</v>
       </c>
     </row>
     <row r="183">
@@ -3470,10 +3470,10 @@
         <v>0.5613354582911551</v>
       </c>
       <c r="C185" t="n">
-        <v>0.3907337128399747</v>
+        <v>0.3907337128399748</v>
       </c>
       <c r="D185" t="n">
-        <v>0.1706017454511804</v>
+        <v>0.1706017454511803</v>
       </c>
     </row>
     <row r="186">
@@ -3505,7 +3505,7 @@
         <v>0.495627423479911</v>
       </c>
       <c r="D187" t="n">
-        <v>0.07342737624892559</v>
+        <v>0.07342737624892554</v>
       </c>
     </row>
     <row r="188">
@@ -3518,7 +3518,7 @@
         <v>0.5117210979763575</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3317711532174036</v>
+        <v>0.3317711532174035</v>
       </c>
       <c r="D188" t="n">
         <v>0.1799499447589539</v>
@@ -3534,10 +3534,10 @@
         <v>0.2425863285940837</v>
       </c>
       <c r="C189" t="n">
-        <v>0.4789040752657617</v>
+        <v>0.4789040752657616</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.236317746671678</v>
+        <v>-0.2363177466716778</v>
       </c>
     </row>
     <row r="190">
@@ -3550,10 +3550,10 @@
         <v>0.2676401400516573</v>
       </c>
       <c r="C190" t="n">
-        <v>0.449798253413879</v>
+        <v>0.4497982534138792</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.1821581133622218</v>
+        <v>-0.1821581133622219</v>
       </c>
     </row>
     <row r="191">
@@ -3582,10 +3582,10 @@
         <v>0.3579790027277858</v>
       </c>
       <c r="C192" t="n">
-        <v>0.4932440484375144</v>
+        <v>0.4932440484375142</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.1352650457097286</v>
+        <v>-0.1352650457097284</v>
       </c>
     </row>
     <row r="193">
@@ -3598,10 +3598,10 @@
         <v>0.2457170183017885</v>
       </c>
       <c r="C193" t="n">
-        <v>0.5387749146721179</v>
+        <v>0.5387749146721178</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2930578963703294</v>
+        <v>-0.2930578963703293</v>
       </c>
     </row>
     <row r="194">
@@ -3614,10 +3614,10 @@
         <v>0.3384152476636595</v>
       </c>
       <c r="C194" t="n">
-        <v>0.6939670055337079</v>
+        <v>0.6939670055337078</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.3555517578700484</v>
+        <v>-0.3555517578700483</v>
       </c>
     </row>
     <row r="195">
@@ -3630,7 +3630,7 @@
         <v>0.6307558398144983</v>
       </c>
       <c r="C195" t="n">
-        <v>0.368866246825986</v>
+        <v>0.3688662468259861</v>
       </c>
       <c r="D195" t="n">
         <v>0.2618895929885123</v>
@@ -3678,10 +3678,10 @@
         <v>0.2048307869197235</v>
       </c>
       <c r="C198" t="n">
-        <v>0.5874167728490804</v>
+        <v>0.5874167728490803</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.382585985929357</v>
+        <v>-0.3825859859293569</v>
       </c>
     </row>
     <row r="199">
@@ -3710,10 +3710,10 @@
         <v>0.3353199157175727</v>
       </c>
       <c r="C200" t="n">
-        <v>0.3679258831473995</v>
+        <v>0.3679258831473994</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.03260596742982685</v>
+        <v>-0.03260596742982669</v>
       </c>
     </row>
     <row r="201">
@@ -3726,10 +3726,10 @@
         <v>0.2681894949034624</v>
       </c>
       <c r="C201" t="n">
-        <v>0.5037247874060018</v>
+        <v>0.5037247874060019</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.2355352925025394</v>
+        <v>-0.2355352925025395</v>
       </c>
     </row>
     <row r="202">
@@ -3758,10 +3758,10 @@
         <v>0.2845583924702809</v>
       </c>
       <c r="C203" t="n">
-        <v>0.4889509177521718</v>
+        <v>0.4889509177521716</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.2043925252818909</v>
+        <v>-0.2043925252818907</v>
       </c>
     </row>
     <row r="204">
@@ -3771,13 +3771,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.2807292778417272</v>
+        <v>0.2807292778417274</v>
       </c>
       <c r="C204" t="n">
         <v>0.4631967170536595</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.1824674392119323</v>
+        <v>-0.1824674392119321</v>
       </c>
     </row>
     <row r="205">
@@ -3790,10 +3790,10 @@
         <v>0.5800641590592914</v>
       </c>
       <c r="C205" t="n">
-        <v>0.351754072362933</v>
+        <v>0.3517540723629329</v>
       </c>
       <c r="D205" t="n">
-        <v>0.2283100866963584</v>
+        <v>0.2283100866963585</v>
       </c>
     </row>
     <row r="206">

--- a/results/GSE186332/glass_recurrence_score_gse186332_universe.xlsx
+++ b/results/GSE186332/glass_recurrence_score_gse186332_universe.xlsx
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3517171867968008</v>
+        <v>0.3517171867968007</v>
       </c>
       <c r="C2" t="n">
         <v>0.6145295737119845</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2628123869151837</v>
+        <v>-0.2628123869151838</v>
       </c>
     </row>
     <row r="3">
@@ -574,10 +574,10 @@
         <v>0.321586044422444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5835212532885993</v>
+        <v>0.5835212532885994</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2619352088661552</v>
+        <v>-0.2619352088661553</v>
       </c>
     </row>
     <row r="5">
@@ -590,10 +590,10 @@
         <v>0.3679935430616068</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6051091310764605</v>
+        <v>0.6051091310764606</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2371155880148537</v>
+        <v>-0.2371155880148538</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>0.4486436151521541</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1589216799389229</v>
+        <v>-0.1589216799389228</v>
       </c>
     </row>
     <row r="7">
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4381573106100785</v>
+        <v>0.4381573106100786</v>
       </c>
       <c r="C7" t="n">
         <v>0.443945616270507</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.005788305660428594</v>
+        <v>-0.005788305660428428</v>
       </c>
     </row>
     <row r="8">
@@ -641,7 +641,7 @@
         <v>0.497803017108355</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1735073022508054</v>
+        <v>-0.1735073022508053</v>
       </c>
     </row>
     <row r="9">
@@ -654,10 +654,10 @@
         <v>0.7541570469546709</v>
       </c>
       <c r="C9" t="n">
-        <v>0.293325098467001</v>
+        <v>0.2933250984670009</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4608319484876699</v>
+        <v>0.46083194848767</v>
       </c>
     </row>
     <row r="10">
@@ -670,10 +670,10 @@
         <v>0.4248649748195991</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6310428488054096</v>
+        <v>0.6310428488054097</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2061778739858106</v>
+        <v>-0.2061778739858107</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +689,7 @@
         <v>0.3674919866653222</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2550180739274048</v>
+        <v>0.2550180739274049</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>0.5388322073414062</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2249146502920944</v>
+        <v>-0.2249146502920945</v>
       </c>
     </row>
     <row r="13">
@@ -750,10 +750,10 @@
         <v>0.4126455943137735</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5640593154824655</v>
+        <v>0.5640593154824654</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.151413721168692</v>
+        <v>-0.1514137211686918</v>
       </c>
     </row>
     <row r="16">
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4155030252711961</v>
+        <v>0.4155030252711962</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5398168773509093</v>
+        <v>0.5398168773509092</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1243138520797132</v>
+        <v>-0.124313852079713</v>
       </c>
     </row>
     <row r="17">
@@ -782,10 +782,10 @@
         <v>0.3484435382381096</v>
       </c>
       <c r="C17" t="n">
-        <v>0.628466206491947</v>
+        <v>0.6284662064919468</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2800226682538373</v>
+        <v>-0.2800226682538372</v>
       </c>
     </row>
     <row r="18">
@@ -801,7 +801,7 @@
         <v>0.4694484931264075</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1039426523297492</v>
+        <v>0.1039426523297491</v>
       </c>
     </row>
     <row r="19">
@@ -830,10 +830,10 @@
         <v>0.5691320629857054</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4480718343126561</v>
+        <v>0.448071834312656</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1210602286730493</v>
+        <v>0.1210602286730494</v>
       </c>
     </row>
     <row r="21">
@@ -849,7 +849,7 @@
         <v>0.4587378195785092</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.03585418895624309</v>
+        <v>-0.03585418895624315</v>
       </c>
     </row>
     <row r="22">
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5968521115786194</v>
+        <v>0.5968521115786193</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4737920413607238</v>
+        <v>0.4737920413607239</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1230600702178956</v>
+        <v>0.1230600702178953</v>
       </c>
     </row>
     <row r="25">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3818247573300787</v>
+        <v>0.3818247573300786</v>
       </c>
       <c r="C25" t="n">
         <v>0.6558146712011904</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2739899138711117</v>
+        <v>-0.2739899138711118</v>
       </c>
     </row>
     <row r="26">
@@ -942,10 +942,10 @@
         <v>0.2333891636754437</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5752161079485558</v>
+        <v>0.5752161079485557</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3418269442731121</v>
+        <v>-0.341826944273112</v>
       </c>
     </row>
     <row r="28">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2903003183508092</v>
+        <v>0.2903003183508093</v>
       </c>
       <c r="C28" t="n">
         <v>0.5984528687585366</v>
@@ -1022,7 +1022,7 @@
         <v>0.6906195858427522</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3694720213159285</v>
+        <v>0.3694720213159286</v>
       </c>
       <c r="D32" t="n">
         <v>0.3211475645268236</v>
@@ -1057,7 +1057,7 @@
         <v>0.423421090424638</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03959141705614772</v>
+        <v>0.03959141705614766</v>
       </c>
     </row>
     <row r="35">
@@ -1102,10 +1102,10 @@
         <v>0.2299166822720985</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4833354722596536</v>
+        <v>0.4833354722596535</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2534187899875551</v>
+        <v>-0.253418789987555</v>
       </c>
     </row>
     <row r="38">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5802619006150068</v>
+        <v>0.5802619006150067</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4882343774349385</v>
+        <v>0.4882343774349384</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09202752318006829</v>
+        <v>0.09202752318006835</v>
       </c>
     </row>
     <row r="39">
@@ -1182,10 +1182,10 @@
         <v>0.2076037521132811</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6198241802564879</v>
+        <v>0.6198241802564878</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4122204281432068</v>
+        <v>-0.4122204281432067</v>
       </c>
     </row>
     <row r="43">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.519596711990079</v>
+        <v>0.5195967119900788</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3175201746586121</v>
+        <v>0.317520174658612</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2020765373314669</v>
+        <v>0.2020765373314668</v>
       </c>
     </row>
     <row r="45">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2778196832730287</v>
+        <v>0.2778196832730288</v>
       </c>
       <c r="C45" t="n">
         <v>0.4899264209345886</v>
@@ -1278,10 +1278,10 @@
         <v>0.2549028338154648</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5939790751893713</v>
+        <v>0.5939790751893714</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3390762413739065</v>
+        <v>-0.3390762413739066</v>
       </c>
     </row>
     <row r="49">
@@ -1326,10 +1326,10 @@
         <v>0.4523353365033095</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4657680120513221</v>
+        <v>0.465768012051322</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.01343267554801264</v>
+        <v>-0.01343267554801247</v>
       </c>
     </row>
     <row r="52">
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3449088533652513</v>
+        <v>0.3449088533652514</v>
       </c>
       <c r="C52" t="n">
         <v>0.602559225341999</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2576503719767477</v>
+        <v>-0.2576503719767476</v>
       </c>
     </row>
     <row r="53">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5184910180372601</v>
+        <v>0.5184910180372602</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5152268636923368</v>
+        <v>0.5152268636923369</v>
       </c>
       <c r="D53" t="n">
         <v>0.00326415434492322</v>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5768151736306179</v>
+        <v>0.576815173630618</v>
       </c>
       <c r="C55" t="n">
         <v>0.3471565266281049</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2296586470025129</v>
+        <v>0.2296586470025131</v>
       </c>
     </row>
     <row r="56">
@@ -1406,10 +1406,10 @@
         <v>0.2557191179417068</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5067215759609127</v>
+        <v>0.5067215759609126</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.2510024580192059</v>
+        <v>-0.2510024580192058</v>
       </c>
     </row>
     <row r="57">
@@ -1438,10 +1438,10 @@
         <v>0.2522558033654478</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4320677000736401</v>
+        <v>0.4320677000736403</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.1798118967081923</v>
+        <v>-0.1798118967081924</v>
       </c>
     </row>
     <row r="59">
@@ -1454,10 +1454,10 @@
         <v>0.2383161149764566</v>
       </c>
       <c r="C59" t="n">
-        <v>0.6466256909495917</v>
+        <v>0.6466256909495915</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4083095759731351</v>
+        <v>-0.408309575973135</v>
       </c>
     </row>
     <row r="60">
@@ -1521,7 +1521,7 @@
         <v>0.5967184286836131</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.3855730074482653</v>
+        <v>-0.3855730074482654</v>
       </c>
     </row>
     <row r="64">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5571169717692281</v>
+        <v>0.5571169717692283</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5156836772421295</v>
+        <v>0.5156836772421296</v>
       </c>
       <c r="D64" t="n">
         <v>0.04143329452709865</v>
@@ -1566,10 +1566,10 @@
         <v>0.2531877641192054</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6337084857318337</v>
+        <v>0.6337084857318336</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.3805207216126283</v>
+        <v>-0.3805207216126282</v>
       </c>
     </row>
     <row r="67">
@@ -1582,10 +1582,10 @@
         <v>0.2324478178368121</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5449778010004064</v>
+        <v>0.5449778010004065</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.3125299831635943</v>
+        <v>-0.3125299831635944</v>
       </c>
     </row>
     <row r="68">
@@ -1646,10 +1646,10 @@
         <v>0.367556372712713</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5785887364139984</v>
+        <v>0.5785887364139983</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.2110323637012855</v>
+        <v>-0.2110323637012854</v>
       </c>
     </row>
     <row r="72">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.2633352234457753</v>
+        <v>0.2633352234457754</v>
       </c>
       <c r="C72" t="n">
         <v>0.4891495323390382</v>
@@ -1678,10 +1678,10 @@
         <v>0.3314074266140927</v>
       </c>
       <c r="C73" t="n">
-        <v>0.4560916621596434</v>
+        <v>0.4560916621596435</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.1246842355455507</v>
+        <v>-0.1246842355455508</v>
       </c>
     </row>
     <row r="74">
@@ -1691,13 +1691,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4612053329980894</v>
+        <v>0.4612053329980893</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4954570732765601</v>
+        <v>0.4954570732765602</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.03425174027847078</v>
+        <v>-0.03425174027847089</v>
       </c>
     </row>
     <row r="75">
@@ -1710,10 +1710,10 @@
         <v>0.4190361823395401</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6042906098078938</v>
+        <v>0.604290609807894</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.1852544274683537</v>
+        <v>-0.1852544274683539</v>
       </c>
     </row>
     <row r="76">
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.359454425373079</v>
+        <v>0.3594544253730789</v>
       </c>
       <c r="C76" t="n">
         <v>0.6227556551684098</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.2633012297953308</v>
+        <v>-0.2633012297953309</v>
       </c>
     </row>
     <row r="77">
@@ -1742,10 +1742,10 @@
         <v>0.4211855850334524</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5783740798797312</v>
+        <v>0.5783740798797311</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.1571884948462788</v>
+        <v>-0.1571884948462787</v>
       </c>
     </row>
     <row r="78">
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.2068402863716782</v>
+        <v>0.2068402863716781</v>
       </c>
       <c r="C80" t="n">
         <v>0.5344313664378015</v>
@@ -1809,7 +1809,7 @@
         <v>0.3774387579560421</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.1279984800527662</v>
+        <v>-0.1279984800527661</v>
       </c>
     </row>
     <row r="82">
@@ -1838,10 +1838,10 @@
         <v>0.5515640571329046</v>
       </c>
       <c r="C83" t="n">
-        <v>0.354916245756523</v>
+        <v>0.3549162457565229</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1966478113763816</v>
+        <v>0.1966478113763817</v>
       </c>
     </row>
     <row r="84">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.232781752252093</v>
+        <v>0.2327817522520929</v>
       </c>
       <c r="C85" t="n">
         <v>0.4252613309621807</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.1924795787100878</v>
+        <v>-0.1924795787100877</v>
       </c>
     </row>
     <row r="86">
@@ -1899,13 +1899,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5148731769472633</v>
+        <v>0.5148731769472632</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5051700904765832</v>
+        <v>0.5051700904765833</v>
       </c>
       <c r="D87" t="n">
-        <v>0.009703086470680078</v>
+        <v>0.009703086470679856</v>
       </c>
     </row>
     <row r="88">
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7412209078738243</v>
+        <v>0.7412209078738242</v>
       </c>
       <c r="C88" t="n">
         <v>0.2849576950929975</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4562632127808269</v>
+        <v>0.4562632127808268</v>
       </c>
     </row>
     <row r="89">
@@ -1934,10 +1934,10 @@
         <v>0.224397161077303</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5278919811652258</v>
+        <v>0.527891981165226</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.3034948200879228</v>
+        <v>-0.3034948200879229</v>
       </c>
     </row>
     <row r="90">
@@ -1950,10 +1950,10 @@
         <v>0.2240195751044691</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4920527428674447</v>
+        <v>0.4920527428674446</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.2680331677629756</v>
+        <v>-0.2680331677629755</v>
       </c>
     </row>
     <row r="91">
@@ -1969,7 +1969,7 @@
         <v>0.4011392074361301</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3193987194379076</v>
+        <v>0.3193987194379077</v>
       </c>
     </row>
     <row r="92">
@@ -1982,10 +1982,10 @@
         <v>0.2299406906287527</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6353023677914365</v>
+        <v>0.6353023677914363</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.4053616771626838</v>
+        <v>-0.4053616771626837</v>
       </c>
     </row>
     <row r="93">
@@ -2014,10 +2014,10 @@
         <v>0.2000339172602187</v>
       </c>
       <c r="C94" t="n">
-        <v>0.5942380380545548</v>
+        <v>0.5942380380545549</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.3942041207943361</v>
+        <v>-0.3942041207943362</v>
       </c>
     </row>
     <row r="95">
@@ -2046,10 +2046,10 @@
         <v>0.3378294437612976</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5266494941439253</v>
+        <v>0.5266494941439254</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.1888200503826277</v>
+        <v>-0.1888200503826278</v>
       </c>
     </row>
     <row r="97">
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.4870902701114729</v>
+        <v>0.487090270111473</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3997821350762527</v>
+        <v>0.3997821350762528</v>
       </c>
       <c r="D97" t="n">
         <v>0.08730813503522022</v>
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5028030847682692</v>
+        <v>0.5028030847682693</v>
       </c>
       <c r="C98" t="n">
         <v>0.432867505736906</v>
       </c>
       <c r="D98" t="n">
-        <v>0.06993557903136316</v>
+        <v>0.06993557903136327</v>
       </c>
     </row>
     <row r="99">
@@ -2110,10 +2110,10 @@
         <v>0.395217709960718</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6453499741801038</v>
+        <v>0.6453499741801036</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.2501322642193858</v>
+        <v>-0.2501322642193857</v>
       </c>
     </row>
     <row r="101">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4450228275820224</v>
+        <v>0.4450228275820223</v>
       </c>
       <c r="C101" t="n">
         <v>0.3237096926974</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1213131348846225</v>
+        <v>0.1213131348846223</v>
       </c>
     </row>
     <row r="102">
@@ -2158,10 +2158,10 @@
         <v>0.4061419487539445</v>
       </c>
       <c r="C103" t="n">
-        <v>0.491958400938683</v>
+        <v>0.4919584009386831</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.08581645218473855</v>
+        <v>-0.08581645218473866</v>
       </c>
     </row>
     <row r="104">
@@ -2190,10 +2190,10 @@
         <v>0.5644639654209821</v>
       </c>
       <c r="C105" t="n">
-        <v>0.5441772314348835</v>
+        <v>0.5441772314348834</v>
       </c>
       <c r="D105" t="n">
-        <v>0.02028673398609859</v>
+        <v>0.0202867339860987</v>
       </c>
     </row>
     <row r="106">
@@ -2257,7 +2257,7 @@
         <v>0.3697737627075141</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3393601947557891</v>
+        <v>0.3393601947557892</v>
       </c>
     </row>
     <row r="110">
@@ -2302,10 +2302,10 @@
         <v>0.2153582330547927</v>
       </c>
       <c r="C112" t="n">
-        <v>0.5139251742461048</v>
+        <v>0.5139251742461047</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.2985669411913121</v>
+        <v>-0.298566941191312</v>
       </c>
     </row>
     <row r="113">
@@ -2318,10 +2318,10 @@
         <v>0.4670114266682207</v>
       </c>
       <c r="C113" t="n">
-        <v>0.5966145379766369</v>
+        <v>0.5966145379766368</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.1296031113084162</v>
+        <v>-0.1296031113084161</v>
       </c>
     </row>
     <row r="114">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5158725793574402</v>
+        <v>0.5158725793574404</v>
       </c>
       <c r="C115" t="n">
         <v>0.4944678198535141</v>
       </c>
       <c r="D115" t="n">
-        <v>0.02140475950392612</v>
+        <v>0.02140475950392629</v>
       </c>
     </row>
     <row r="116">
@@ -2382,10 +2382,10 @@
         <v>0.2166784744129847</v>
       </c>
       <c r="C117" t="n">
-        <v>0.5250216184338781</v>
+        <v>0.5250216184338782</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.3083431440208934</v>
+        <v>-0.3083431440208935</v>
       </c>
     </row>
     <row r="118">
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6548157053065888</v>
+        <v>0.6548157053065889</v>
       </c>
       <c r="C119" t="n">
         <v>0.3615755636834756</v>
       </c>
       <c r="D119" t="n">
-        <v>0.2932401416231132</v>
+        <v>0.2932401416231133</v>
       </c>
     </row>
     <row r="120">
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5389596698894612</v>
+        <v>0.5389596698894611</v>
       </c>
       <c r="C120" t="n">
         <v>0.5530873873626122</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.014127717473151</v>
+        <v>-0.01412771747315111</v>
       </c>
     </row>
     <row r="121">
@@ -2462,10 +2462,10 @@
         <v>0.6519285912900301</v>
       </c>
       <c r="C122" t="n">
-        <v>0.4405122575756188</v>
+        <v>0.4405122575756187</v>
       </c>
       <c r="D122" t="n">
-        <v>0.2114163337144113</v>
+        <v>0.2114163337144114</v>
       </c>
     </row>
     <row r="123">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.7286654103748403</v>
+        <v>0.7286654103748402</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3728797892852014</v>
+        <v>0.3728797892852013</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3557856210896389</v>
+        <v>0.355785621089639</v>
       </c>
     </row>
     <row r="124">
@@ -2494,10 +2494,10 @@
         <v>0.5156610875610957</v>
       </c>
       <c r="C124" t="n">
-        <v>0.4113353928138187</v>
+        <v>0.4113353928138186</v>
       </c>
       <c r="D124" t="n">
-        <v>0.104325694747277</v>
+        <v>0.1043256947472772</v>
       </c>
     </row>
     <row r="125">
@@ -2510,7 +2510,7 @@
         <v>0.2810848197779969</v>
       </c>
       <c r="C125" t="n">
-        <v>0.5589770737654576</v>
+        <v>0.5589770737654575</v>
       </c>
       <c r="D125" t="n">
         <v>-0.2778922539874606</v>
@@ -2526,10 +2526,10 @@
         <v>0.2906595706694708</v>
       </c>
       <c r="C126" t="n">
-        <v>0.554996379103301</v>
+        <v>0.5549963791033009</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.2643368084338302</v>
+        <v>-0.2643368084338301</v>
       </c>
     </row>
     <row r="127">
@@ -2558,10 +2558,10 @@
         <v>0.3578467385084001</v>
       </c>
       <c r="C128" t="n">
-        <v>0.6169946862958992</v>
+        <v>0.616994686295899</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.2591479477874991</v>
+        <v>-0.2591479477874989</v>
       </c>
     </row>
     <row r="129">
@@ -2574,10 +2574,10 @@
         <v>0.4436491130658278</v>
       </c>
       <c r="C129" t="n">
-        <v>0.4408269853055761</v>
+        <v>0.4408269853055762</v>
       </c>
       <c r="D129" t="n">
-        <v>0.002822127760251703</v>
+        <v>0.002822127760251592</v>
       </c>
     </row>
     <row r="130">
@@ -2590,10 +2590,10 @@
         <v>0.3982480010860507</v>
       </c>
       <c r="C130" t="n">
-        <v>0.6174430969208627</v>
+        <v>0.6174430969208626</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.219195095834812</v>
+        <v>-0.2191950958348119</v>
       </c>
     </row>
     <row r="131">
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6401740998721447</v>
+        <v>0.6401740998721446</v>
       </c>
       <c r="C131" t="n">
-        <v>0.4853575215344046</v>
+        <v>0.4853575215344047</v>
       </c>
       <c r="D131" t="n">
-        <v>0.15481657833774</v>
+        <v>0.1548165783377399</v>
       </c>
     </row>
     <row r="132">
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.2495821454653235</v>
+        <v>0.2495821454653234</v>
       </c>
       <c r="C132" t="n">
-        <v>0.5333703062025807</v>
+        <v>0.5333703062025809</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.2837881607372573</v>
+        <v>-0.2837881607372574</v>
       </c>
     </row>
     <row r="133">
@@ -2654,10 +2654,10 @@
         <v>0.3872696343614584</v>
       </c>
       <c r="C134" t="n">
-        <v>0.4871511640342595</v>
+        <v>0.4871511640342594</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.09988152967280106</v>
+        <v>-0.09988152967280095</v>
       </c>
     </row>
     <row r="135">
@@ -2670,10 +2670,10 @@
         <v>0.271510068886523</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6528514943455955</v>
+        <v>0.6528514943455954</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.3813414254590726</v>
+        <v>-0.3813414254590725</v>
       </c>
     </row>
     <row r="136">
@@ -2699,13 +2699,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.264622289620227</v>
+        <v>0.2646222896202271</v>
       </c>
       <c r="C137" t="n">
-        <v>0.6486813519236587</v>
+        <v>0.6486813519236586</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.3840590623034317</v>
+        <v>-0.3840590623034315</v>
       </c>
     </row>
     <row r="138">
@@ -2718,10 +2718,10 @@
         <v>0.3263348973686405</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4071858757528256</v>
+        <v>0.4071858757528258</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.08085097838418515</v>
+        <v>-0.08085097838418531</v>
       </c>
     </row>
     <row r="139">
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4394157850143329</v>
+        <v>0.4394157850143331</v>
       </c>
       <c r="C140" t="n">
-        <v>0.4099397433899539</v>
+        <v>0.4099397433899538</v>
       </c>
       <c r="D140" t="n">
-        <v>0.029476041624379</v>
+        <v>0.02947604162437928</v>
       </c>
     </row>
     <row r="141">
@@ -2782,10 +2782,10 @@
         <v>0.2585595247916838</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4555523471660755</v>
+        <v>0.4555523471660753</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.1969928223743916</v>
+        <v>-0.1969928223743915</v>
       </c>
     </row>
     <row r="143">
@@ -2814,10 +2814,10 @@
         <v>0.2422277310487854</v>
       </c>
       <c r="C144" t="n">
-        <v>0.5846044666892781</v>
+        <v>0.584604466689278</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.3423767356404927</v>
+        <v>-0.3423767356404926</v>
       </c>
     </row>
     <row r="145">
@@ -2862,10 +2862,10 @@
         <v>0.4098737204091548</v>
       </c>
       <c r="C147" t="n">
-        <v>0.5642113320316439</v>
+        <v>0.564211332031644</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.1543376116224891</v>
+        <v>-0.1543376116224892</v>
       </c>
     </row>
     <row r="148">
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.2310769406718586</v>
+        <v>0.2310769406718585</v>
       </c>
       <c r="C148" t="n">
         <v>0.5595744453305711</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.3284975046587125</v>
+        <v>-0.3284975046587126</v>
       </c>
     </row>
     <row r="149">
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.3421190823220358</v>
+        <v>0.3421190823220359</v>
       </c>
       <c r="C149" t="n">
-        <v>0.6288214210415348</v>
+        <v>0.628821421041535</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.286702338719499</v>
+        <v>-0.2867023387194992</v>
       </c>
     </row>
     <row r="150">
@@ -2926,10 +2926,10 @@
         <v>0.1959804336258424</v>
       </c>
       <c r="C151" t="n">
-        <v>0.5528528693696584</v>
+        <v>0.5528528693696585</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.356872435743816</v>
+        <v>-0.3568724357438161</v>
       </c>
     </row>
     <row r="152">
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.476424012023385</v>
+        <v>0.4764240120233851</v>
       </c>
       <c r="C155" t="n">
         <v>0.45196658997088</v>
       </c>
       <c r="D155" t="n">
-        <v>0.02445742205250501</v>
+        <v>0.02445742205250506</v>
       </c>
     </row>
     <row r="156">
@@ -3022,10 +3022,10 @@
         <v>0.294806250379223</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6016135143476121</v>
+        <v>0.6016135143476122</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.3068072639683891</v>
+        <v>-0.3068072639683893</v>
       </c>
     </row>
     <row r="158">
@@ -3041,7 +3041,7 @@
         <v>0.3459995966596082</v>
       </c>
       <c r="D158" t="n">
-        <v>0.3884099221736381</v>
+        <v>0.388409922173638</v>
       </c>
     </row>
     <row r="159">
@@ -3070,10 +3070,10 @@
         <v>0.2029077175517238</v>
       </c>
       <c r="C160" t="n">
-        <v>0.4514761647217714</v>
+        <v>0.4514761647217715</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.2485684471700476</v>
+        <v>-0.2485684471700477</v>
       </c>
     </row>
     <row r="161">
@@ -3083,13 +3083,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.3636654911302218</v>
+        <v>0.3636654911302217</v>
       </c>
       <c r="C161" t="n">
-        <v>0.5402973718706743</v>
+        <v>0.5402973718706744</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.1766318807404525</v>
+        <v>-0.1766318807404527</v>
       </c>
     </row>
     <row r="162">
@@ -3118,10 +3118,10 @@
         <v>0.2608778590133264</v>
       </c>
       <c r="C163" t="n">
-        <v>0.5278113894770937</v>
+        <v>0.5278113894770936</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.2669335304637673</v>
+        <v>-0.2669335304637672</v>
       </c>
     </row>
     <row r="164">
@@ -3163,13 +3163,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.4330893647781693</v>
+        <v>0.4330893647781694</v>
       </c>
       <c r="C166" t="n">
-        <v>0.5378819129334762</v>
+        <v>0.5378819129334764</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.1047925481553069</v>
+        <v>-0.104792548155307</v>
       </c>
     </row>
     <row r="167">
@@ -3201,7 +3201,7 @@
         <v>0.4900906599198819</v>
       </c>
       <c r="D168" t="n">
-        <v>0.05492828267351824</v>
+        <v>0.05492828267351818</v>
       </c>
     </row>
     <row r="169">
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.2233130746454729</v>
+        <v>0.223313074645473</v>
       </c>
       <c r="C169" t="n">
         <v>0.4582932284648314</v>
@@ -3230,10 +3230,10 @@
         <v>0.5346006253522135</v>
       </c>
       <c r="C170" t="n">
-        <v>0.472413961688774</v>
+        <v>0.4724139616887739</v>
       </c>
       <c r="D170" t="n">
-        <v>0.06218666366343956</v>
+        <v>0.06218666366343961</v>
       </c>
     </row>
     <row r="171">
@@ -3246,10 +3246,10 @@
         <v>0.3756674868794331</v>
       </c>
       <c r="C171" t="n">
-        <v>0.4824760822203279</v>
+        <v>0.4824760822203277</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.1068085953408948</v>
+        <v>-0.1068085953408945</v>
       </c>
     </row>
     <row r="172">
@@ -3262,7 +3262,7 @@
         <v>0.4987777563885146</v>
       </c>
       <c r="C172" t="n">
-        <v>0.3166397773072139</v>
+        <v>0.316639777307214</v>
       </c>
       <c r="D172" t="n">
         <v>0.1821379790813006</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.3731151803093061</v>
+        <v>0.3731151803093062</v>
       </c>
       <c r="C173" t="n">
-        <v>0.4728745947498527</v>
+        <v>0.4728745947498526</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.09975941444054653</v>
+        <v>-0.09975941444054642</v>
       </c>
     </row>
     <row r="174">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.3461594704891463</v>
+        <v>0.3461594704891462</v>
       </c>
       <c r="C175" t="n">
         <v>0.3706125273858959</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.02445305689674959</v>
+        <v>-0.02445305689674965</v>
       </c>
     </row>
     <row r="176">
@@ -3326,10 +3326,10 @@
         <v>0.2082480491027641</v>
       </c>
       <c r="C176" t="n">
-        <v>0.5553011761039153</v>
+        <v>0.5553011761039152</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.3470531270011512</v>
+        <v>-0.3470531270011511</v>
       </c>
     </row>
     <row r="177">
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.3020002453217535</v>
+        <v>0.3020002453217534</v>
       </c>
       <c r="C177" t="n">
-        <v>0.5702981052168413</v>
+        <v>0.5702981052168412</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.2682978598950879</v>
+        <v>-0.2682978598950878</v>
       </c>
     </row>
     <row r="178">
@@ -3355,13 +3355,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.6952676036910012</v>
+        <v>0.695267603691001</v>
       </c>
       <c r="C178" t="n">
         <v>0.3129134620966978</v>
       </c>
       <c r="D178" t="n">
-        <v>0.3823541415943034</v>
+        <v>0.3823541415943032</v>
       </c>
     </row>
     <row r="179">
@@ -3505,7 +3505,7 @@
         <v>0.495627423479911</v>
       </c>
       <c r="D187" t="n">
-        <v>0.07342737624892554</v>
+        <v>0.07342737624892559</v>
       </c>
     </row>
     <row r="188">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.5117210979763575</v>
+        <v>0.5117210979763573</v>
       </c>
       <c r="C188" t="n">
         <v>0.3317711532174035</v>
       </c>
       <c r="D188" t="n">
-        <v>0.1799499447589539</v>
+        <v>0.1799499447589538</v>
       </c>
     </row>
     <row r="189">
@@ -3537,7 +3537,7 @@
         <v>0.4789040752657616</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.2363177466716778</v>
+        <v>-0.2363177466716779</v>
       </c>
     </row>
     <row r="190">
@@ -3550,7 +3550,7 @@
         <v>0.2676401400516573</v>
       </c>
       <c r="C190" t="n">
-        <v>0.4497982534138792</v>
+        <v>0.4497982534138791</v>
       </c>
       <c r="D190" t="n">
         <v>-0.1821581133622219</v>
@@ -3582,10 +3582,10 @@
         <v>0.3579790027277858</v>
       </c>
       <c r="C192" t="n">
-        <v>0.4932440484375142</v>
+        <v>0.4932440484375143</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.1352650457097284</v>
+        <v>-0.1352650457097285</v>
       </c>
     </row>
     <row r="193">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2457170183017885</v>
+        <v>0.2457170183017886</v>
       </c>
       <c r="C193" t="n">
         <v>0.5387749146721178</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2930578963703293</v>
+        <v>-0.2930578963703292</v>
       </c>
     </row>
     <row r="194">
@@ -3614,10 +3614,10 @@
         <v>0.3384152476636595</v>
       </c>
       <c r="C194" t="n">
-        <v>0.6939670055337078</v>
+        <v>0.693967005533708</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.3555517578700483</v>
+        <v>-0.3555517578700486</v>
       </c>
     </row>
     <row r="195">
@@ -3643,13 +3643,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.6882768067488799</v>
+        <v>0.68827680674888</v>
       </c>
       <c r="C196" t="n">
         <v>0.3320931380188042</v>
       </c>
       <c r="D196" t="n">
-        <v>0.3561836687300757</v>
+        <v>0.3561836687300758</v>
       </c>
     </row>
     <row r="197">
@@ -3678,10 +3678,10 @@
         <v>0.2048307869197235</v>
       </c>
       <c r="C198" t="n">
-        <v>0.5874167728490803</v>
+        <v>0.5874167728490804</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.3825859859293569</v>
+        <v>-0.382585985929357</v>
       </c>
     </row>
     <row r="199">
@@ -3694,10 +3694,10 @@
         <v>0.4725839845054432</v>
       </c>
       <c r="C199" t="n">
-        <v>0.4719938154473258</v>
+        <v>0.4719938154473259</v>
       </c>
       <c r="D199" t="n">
-        <v>0.0005901690581173735</v>
+        <v>0.000590169058117318</v>
       </c>
     </row>
     <row r="200">
@@ -3710,10 +3710,10 @@
         <v>0.3353199157175727</v>
       </c>
       <c r="C200" t="n">
-        <v>0.3679258831473994</v>
+        <v>0.3679258831473995</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.03260596742982669</v>
+        <v>-0.03260596742982685</v>
       </c>
     </row>
     <row r="201">
@@ -3726,10 +3726,10 @@
         <v>0.2681894949034624</v>
       </c>
       <c r="C201" t="n">
-        <v>0.5037247874060019</v>
+        <v>0.5037247874060018</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.2355352925025395</v>
+        <v>-0.2355352925025394</v>
       </c>
     </row>
     <row r="202">
@@ -3739,13 +3739,13 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.7203790352045446</v>
+        <v>0.7203790352045447</v>
       </c>
       <c r="C202" t="n">
-        <v>0.3054356229011786</v>
+        <v>0.3054356229011785</v>
       </c>
       <c r="D202" t="n">
-        <v>0.414943412303366</v>
+        <v>0.4149434123033662</v>
       </c>
     </row>
     <row r="203">
@@ -3758,10 +3758,10 @@
         <v>0.2845583924702809</v>
       </c>
       <c r="C203" t="n">
-        <v>0.4889509177521716</v>
+        <v>0.4889509177521718</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.2043925252818907</v>
+        <v>-0.2043925252818909</v>
       </c>
     </row>
     <row r="204">
@@ -3774,10 +3774,10 @@
         <v>0.2807292778417274</v>
       </c>
       <c r="C204" t="n">
-        <v>0.4631967170536595</v>
+        <v>0.4631967170536596</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.1824674392119321</v>
+        <v>-0.1824674392119323</v>
       </c>
     </row>
     <row r="205">
@@ -3790,10 +3790,10 @@
         <v>0.5800641590592914</v>
       </c>
       <c r="C205" t="n">
-        <v>0.3517540723629329</v>
+        <v>0.351754072362933</v>
       </c>
       <c r="D205" t="n">
-        <v>0.2283100866963585</v>
+        <v>0.2283100866963584</v>
       </c>
     </row>
     <row r="206">
@@ -3806,10 +3806,10 @@
         <v>0.6630496986078209</v>
       </c>
       <c r="C206" t="n">
-        <v>0.3522360946872126</v>
+        <v>0.3522360946872125</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3108136039206083</v>
+        <v>0.3108136039206084</v>
       </c>
     </row>
     <row r="207">
@@ -3822,10 +3822,10 @@
         <v>0.3527840308633973</v>
       </c>
       <c r="C207" t="n">
-        <v>0.5392355477331965</v>
+        <v>0.5392355477331964</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.1864515168697992</v>
+        <v>-0.1864515168697991</v>
       </c>
     </row>
   </sheetData>

--- a/results/GSE186332/glass_recurrence_score_gse186332_universe.xlsx
+++ b/results/GSE186332/glass_recurrence_score_gse186332_universe.xlsx
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3517171867968007</v>
+        <v>0.3517171867968008</v>
       </c>
       <c r="C2" t="n">
         <v>0.6145295737119845</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2628123869151838</v>
+        <v>-0.2628123869151837</v>
       </c>
     </row>
     <row r="3">
@@ -558,10 +558,10 @@
         <v>0.3666726469300514</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4497405787934622</v>
+        <v>0.4497405787934624</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.08306793186341083</v>
+        <v>-0.08306793186341094</v>
       </c>
     </row>
     <row r="4">
@@ -574,10 +574,10 @@
         <v>0.321586044422444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5835212532885994</v>
+        <v>0.5835212532885992</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2619352088661553</v>
+        <v>-0.2619352088661551</v>
       </c>
     </row>
     <row r="5">
@@ -609,7 +609,7 @@
         <v>0.4486436151521541</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1589216799389228</v>
+        <v>-0.1589216799389229</v>
       </c>
     </row>
     <row r="7">
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4381573106100786</v>
+        <v>0.4381573106100785</v>
       </c>
       <c r="C7" t="n">
-        <v>0.443945616270507</v>
+        <v>0.4439456162705069</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.005788305660428428</v>
+        <v>-0.005788305660428483</v>
       </c>
     </row>
     <row r="8">
@@ -641,7 +641,7 @@
         <v>0.497803017108355</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1735073022508053</v>
+        <v>-0.1735073022508054</v>
       </c>
     </row>
     <row r="9">
@@ -654,10 +654,10 @@
         <v>0.7541570469546709</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2933250984670009</v>
+        <v>0.293325098467001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.46083194848767</v>
+        <v>0.4608319484876699</v>
       </c>
     </row>
     <row r="10">
@@ -683,13 +683,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6225100605927271</v>
+        <v>0.622510060592727</v>
       </c>
       <c r="C11" t="n">
         <v>0.3674919866653222</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2550180739274049</v>
+        <v>0.2550180739274047</v>
       </c>
     </row>
     <row r="12">
@@ -718,10 +718,10 @@
         <v>0.2518140496030109</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5261689996241601</v>
+        <v>0.52616899962416</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2743549500211492</v>
+        <v>-0.2743549500211491</v>
       </c>
     </row>
     <row r="14">
@@ -750,10 +750,10 @@
         <v>0.4126455943137735</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5640593154824654</v>
+        <v>0.5640593154824655</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1514137211686918</v>
+        <v>-0.151413721168692</v>
       </c>
     </row>
     <row r="16">
@@ -766,10 +766,10 @@
         <v>0.4155030252711962</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5398168773509092</v>
+        <v>0.5398168773509093</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.124313852079713</v>
+        <v>-0.1243138520797131</v>
       </c>
     </row>
     <row r="17">
@@ -779,13 +779,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3484435382381096</v>
+        <v>0.3484435382381097</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6284662064919468</v>
+        <v>0.628466206491947</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2800226682538372</v>
+        <v>-0.2800226682538373</v>
       </c>
     </row>
     <row r="18">
@@ -830,10 +830,10 @@
         <v>0.5691320629857054</v>
       </c>
       <c r="C20" t="n">
-        <v>0.448071834312656</v>
+        <v>0.4480718343126561</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1210602286730494</v>
+        <v>0.1210602286730493</v>
       </c>
     </row>
     <row r="21">
@@ -846,10 +846,10 @@
         <v>0.4228836306222661</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4587378195785092</v>
+        <v>0.4587378195785093</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.03585418895624315</v>
+        <v>-0.0358541889562432</v>
       </c>
     </row>
     <row r="22">
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5897015499358541</v>
+        <v>0.589701549935854</v>
       </c>
       <c r="C22" t="n">
         <v>0.3666261034568105</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2230754464790436</v>
+        <v>0.2230754464790435</v>
       </c>
     </row>
     <row r="23">
@@ -894,10 +894,10 @@
         <v>0.5968521115786193</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4737920413607239</v>
+        <v>0.4737920413607238</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1230600702178953</v>
+        <v>0.1230600702178955</v>
       </c>
     </row>
     <row r="25">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3818247573300786</v>
+        <v>0.3818247573300787</v>
       </c>
       <c r="C25" t="n">
         <v>0.6558146712011904</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2739899138711118</v>
+        <v>-0.2739899138711117</v>
       </c>
     </row>
     <row r="26">
@@ -926,10 +926,10 @@
         <v>0.5203387884684807</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5626781802014869</v>
+        <v>0.5626781802014867</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04233939173300616</v>
+        <v>-0.04233939173300605</v>
       </c>
     </row>
     <row r="27">
@@ -942,10 +942,10 @@
         <v>0.2333891636754437</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5752161079485557</v>
+        <v>0.5752161079485559</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.341826944273112</v>
+        <v>-0.3418269442731122</v>
       </c>
     </row>
     <row r="28">
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2903003183508093</v>
+        <v>0.2903003183508092</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5984528687585366</v>
+        <v>0.5984528687585365</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3081525504077274</v>
+        <v>-0.3081525504077273</v>
       </c>
     </row>
     <row r="29">
@@ -974,10 +974,10 @@
         <v>0.5380892578318534</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5181923322547034</v>
+        <v>0.5181923322547033</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01989692557714995</v>
+        <v>0.01989692557715006</v>
       </c>
     </row>
     <row r="30">
@@ -1054,10 +1054,10 @@
         <v>0.4630125074807857</v>
       </c>
       <c r="C34" t="n">
-        <v>0.423421090424638</v>
+        <v>0.4234210904246379</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03959141705614766</v>
+        <v>0.03959141705614783</v>
       </c>
     </row>
     <row r="35">
@@ -1102,10 +1102,10 @@
         <v>0.2299166822720985</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4833354722596535</v>
+        <v>0.4833354722596533</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.253418789987555</v>
+        <v>-0.2534187899875548</v>
       </c>
     </row>
     <row r="38">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5802619006150067</v>
+        <v>0.5802619006150068</v>
       </c>
       <c r="C38" t="n">
         <v>0.4882343774349384</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09202752318006835</v>
+        <v>0.09202752318006846</v>
       </c>
     </row>
     <row r="39">
@@ -1150,7 +1150,7 @@
         <v>0.6602284984431672</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4660495100330923</v>
+        <v>0.4660495100330922</v>
       </c>
       <c r="D40" t="n">
         <v>0.194178988410075</v>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2076037521132811</v>
+        <v>0.207603752113281</v>
       </c>
       <c r="C42" t="n">
         <v>0.6198241802564878</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4122204281432067</v>
+        <v>-0.4122204281432068</v>
       </c>
     </row>
     <row r="43">
@@ -1198,10 +1198,10 @@
         <v>0.3322547033461974</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4653448102008452</v>
+        <v>0.4653448102008451</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1330901068546478</v>
+        <v>-0.1330901068546477</v>
       </c>
     </row>
     <row r="44">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5195967119900788</v>
+        <v>0.519596711990079</v>
       </c>
       <c r="C44" t="n">
-        <v>0.317520174658612</v>
+        <v>0.3175201746586121</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2020765373314668</v>
+        <v>0.2020765373314669</v>
       </c>
     </row>
     <row r="45">
@@ -1230,7 +1230,7 @@
         <v>0.2778196832730288</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4899264209345886</v>
+        <v>0.4899264209345887</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2121067376615599</v>
@@ -1262,10 +1262,10 @@
         <v>0.4909150195842713</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6150467355400941</v>
+        <v>0.6150467355400943</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1241317159558229</v>
+        <v>-0.124131715955823</v>
       </c>
     </row>
     <row r="48">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2549028338154648</v>
+        <v>0.2549028338154647</v>
       </c>
       <c r="C48" t="n">
         <v>0.5939790751893714</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3390762413739066</v>
+        <v>-0.3390762413739067</v>
       </c>
     </row>
     <row r="49">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4523353365033095</v>
+        <v>0.4523353365033094</v>
       </c>
       <c r="C51" t="n">
         <v>0.465768012051322</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.01343267554801247</v>
+        <v>-0.01343267554801258</v>
       </c>
     </row>
     <row r="52">
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3449088533652514</v>
+        <v>0.3449088533652513</v>
       </c>
       <c r="C52" t="n">
         <v>0.602559225341999</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2576503719767476</v>
+        <v>-0.2576503719767477</v>
       </c>
     </row>
     <row r="53">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5184910180372602</v>
+        <v>0.5184910180372601</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5152268636923369</v>
+        <v>0.5152268636923368</v>
       </c>
       <c r="D53" t="n">
         <v>0.00326415434492322</v>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.576815173630618</v>
+        <v>0.5768151736306179</v>
       </c>
       <c r="C55" t="n">
         <v>0.3471565266281049</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2296586470025131</v>
+        <v>0.229658647002513</v>
       </c>
     </row>
     <row r="56">
@@ -1406,10 +1406,10 @@
         <v>0.2557191179417068</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5067215759609126</v>
+        <v>0.5067215759609127</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.2510024580192058</v>
+        <v>-0.2510024580192059</v>
       </c>
     </row>
     <row r="57">
@@ -1438,10 +1438,10 @@
         <v>0.2522558033654478</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4320677000736403</v>
+        <v>0.4320677000736401</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.1798118967081924</v>
+        <v>-0.1798118967081923</v>
       </c>
     </row>
     <row r="59">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3543419549524657</v>
+        <v>0.3543419549524656</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4804677831862058</v>
+        <v>0.4804677831862057</v>
       </c>
       <c r="D60" t="n">
         <v>-0.1261258282337401</v>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.2190666511267122</v>
+        <v>0.2190666511267121</v>
       </c>
       <c r="C61" t="n">
         <v>0.4959123590218384</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.2768457078951262</v>
+        <v>-0.2768457078951263</v>
       </c>
     </row>
     <row r="62">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5559959997712659</v>
+        <v>0.5559959997712658</v>
       </c>
       <c r="C62" t="n">
         <v>0.3876124082171438</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1683835915541221</v>
+        <v>0.168383591554122</v>
       </c>
     </row>
     <row r="63">
@@ -1518,10 +1518,10 @@
         <v>0.2111454212353478</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5967184286836131</v>
+        <v>0.596718428683613</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.3855730074482654</v>
+        <v>-0.3855730074482653</v>
       </c>
     </row>
     <row r="64">
@@ -1534,10 +1534,10 @@
         <v>0.5571169717692283</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5156836772421296</v>
+        <v>0.5156836772421294</v>
       </c>
       <c r="D64" t="n">
-        <v>0.04143329452709865</v>
+        <v>0.04143329452709887</v>
       </c>
     </row>
     <row r="65">
@@ -1550,10 +1550,10 @@
         <v>0.4236920574681486</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4247097935324979</v>
+        <v>0.424709793532498</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.00101773606434935</v>
+        <v>-0.001017736064349462</v>
       </c>
     </row>
     <row r="66">
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.2531877641192054</v>
+        <v>0.2531877641192055</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6337084857318336</v>
+        <v>0.6337084857318337</v>
       </c>
       <c r="D66" t="n">
         <v>-0.3805207216126282</v>
@@ -1582,10 +1582,10 @@
         <v>0.2324478178368121</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5449778010004065</v>
+        <v>0.5449778010004064</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.3125299831635944</v>
+        <v>-0.3125299831635943</v>
       </c>
     </row>
     <row r="68">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3953477916022261</v>
+        <v>0.395347791602226</v>
       </c>
       <c r="C69" t="n">
         <v>0.4541284333586949</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.05878064175646885</v>
+        <v>-0.05878064175646891</v>
       </c>
     </row>
     <row r="70">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.367556372712713</v>
+        <v>0.3675563727127129</v>
       </c>
       <c r="C71" t="n">
         <v>0.5785887364139983</v>
@@ -1665,7 +1665,7 @@
         <v>0.4891495323390382</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.2258143088932629</v>
+        <v>-0.2258143088932628</v>
       </c>
     </row>
     <row r="73">
@@ -1678,10 +1678,10 @@
         <v>0.3314074266140927</v>
       </c>
       <c r="C73" t="n">
-        <v>0.4560916621596435</v>
+        <v>0.4560916621596433</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.1246842355455508</v>
+        <v>-0.1246842355455506</v>
       </c>
     </row>
     <row r="74">
@@ -1691,13 +1691,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4612053329980893</v>
+        <v>0.4612053329980894</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4954570732765602</v>
+        <v>0.4954570732765601</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.03425174027847089</v>
+        <v>-0.03425174027847078</v>
       </c>
     </row>
     <row r="75">
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4190361823395401</v>
+        <v>0.4190361823395402</v>
       </c>
       <c r="C75" t="n">
-        <v>0.604290609807894</v>
+        <v>0.6042906098078938</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.1852544274683539</v>
+        <v>-0.1852544274683537</v>
       </c>
     </row>
     <row r="76">
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.2068402863716781</v>
+        <v>0.2068402863716782</v>
       </c>
       <c r="C80" t="n">
         <v>0.5344313664378015</v>
@@ -1838,10 +1838,10 @@
         <v>0.5515640571329046</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3549162457565229</v>
+        <v>0.354916245756523</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1966478113763817</v>
+        <v>0.1966478113763816</v>
       </c>
     </row>
     <row r="84">
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5674139376804174</v>
+        <v>0.5674139376804173</v>
       </c>
       <c r="C84" t="n">
         <v>0.3701083518961582</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1973055857842592</v>
+        <v>0.1973055857842591</v>
       </c>
     </row>
     <row r="85">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.2327817522520929</v>
+        <v>0.232781752252093</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4252613309621807</v>
+        <v>0.4252613309621808</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.1924795787100877</v>
+        <v>-0.1924795787100878</v>
       </c>
     </row>
     <row r="86">
@@ -1902,10 +1902,10 @@
         <v>0.5148731769472632</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5051700904765833</v>
+        <v>0.5051700904765832</v>
       </c>
       <c r="D87" t="n">
-        <v>0.009703086470679856</v>
+        <v>0.009703086470679967</v>
       </c>
     </row>
     <row r="88">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7412209078738242</v>
+        <v>0.7412209078738243</v>
       </c>
       <c r="C88" t="n">
         <v>0.2849576950929975</v>
@@ -1950,10 +1950,10 @@
         <v>0.2240195751044691</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4920527428674446</v>
+        <v>0.4920527428674447</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.2680331677629755</v>
+        <v>-0.2680331677629756</v>
       </c>
     </row>
     <row r="91">
@@ -1969,7 +1969,7 @@
         <v>0.4011392074361301</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3193987194379077</v>
+        <v>0.3193987194379076</v>
       </c>
     </row>
     <row r="92">
@@ -2014,10 +2014,10 @@
         <v>0.2000339172602187</v>
       </c>
       <c r="C94" t="n">
-        <v>0.5942380380545549</v>
+        <v>0.5942380380545548</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.3942041207943362</v>
+        <v>-0.3942041207943361</v>
       </c>
     </row>
     <row r="95">
@@ -2030,10 +2030,10 @@
         <v>0.6026551496397219</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3374477108904962</v>
+        <v>0.3374477108904961</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2652074387492257</v>
+        <v>0.2652074387492258</v>
       </c>
     </row>
     <row r="96">
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.3378294437612976</v>
+        <v>0.3378294437612975</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5266494941439254</v>
+        <v>0.5266494941439253</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.1888200503826278</v>
+        <v>-0.1888200503826277</v>
       </c>
     </row>
     <row r="97">
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.487090270111473</v>
+        <v>0.4870902701114729</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3997821350762528</v>
+        <v>0.3997821350762527</v>
       </c>
       <c r="D97" t="n">
         <v>0.08730813503522022</v>
@@ -2078,10 +2078,10 @@
         <v>0.5028030847682693</v>
       </c>
       <c r="C98" t="n">
-        <v>0.432867505736906</v>
+        <v>0.4328675057369059</v>
       </c>
       <c r="D98" t="n">
-        <v>0.06993557903136327</v>
+        <v>0.06993557903136344</v>
       </c>
     </row>
     <row r="99">
@@ -2097,7 +2097,7 @@
         <v>0.4956755493221131</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.227139897567255</v>
+        <v>-0.2271398975672551</v>
       </c>
     </row>
     <row r="100">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.395217709960718</v>
+        <v>0.3952177099607179</v>
       </c>
       <c r="C100" t="n">
         <v>0.6453499741801036</v>
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4450228275820223</v>
+        <v>0.4450228275820224</v>
       </c>
       <c r="C101" t="n">
         <v>0.3237096926974</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1213131348846223</v>
+        <v>0.1213131348846224</v>
       </c>
     </row>
     <row r="102">
@@ -2142,10 +2142,10 @@
         <v>0.2694488423388679</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6047363467749576</v>
+        <v>0.6047363467749575</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.3352875044360897</v>
+        <v>-0.3352875044360896</v>
       </c>
     </row>
     <row r="103">
@@ -2161,7 +2161,7 @@
         <v>0.4919584009386831</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.08581645218473866</v>
+        <v>-0.0858164521847386</v>
       </c>
     </row>
     <row r="104">
@@ -2190,10 +2190,10 @@
         <v>0.5644639654209821</v>
       </c>
       <c r="C105" t="n">
-        <v>0.5441772314348834</v>
+        <v>0.5441772314348835</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0202867339860987</v>
+        <v>0.02028673398609859</v>
       </c>
     </row>
     <row r="106">
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.3660665450534274</v>
+        <v>0.3660665450534273</v>
       </c>
       <c r="C111" t="n">
-        <v>0.5419275392874932</v>
+        <v>0.541927539287493</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.1758609942340658</v>
+        <v>-0.1758609942340657</v>
       </c>
     </row>
     <row r="112">
@@ -2302,10 +2302,10 @@
         <v>0.2153582330547927</v>
       </c>
       <c r="C112" t="n">
-        <v>0.5139251742461047</v>
+        <v>0.5139251742461048</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.298566941191312</v>
+        <v>-0.2985669411913121</v>
       </c>
     </row>
     <row r="113">
@@ -2353,7 +2353,7 @@
         <v>0.4944678198535141</v>
       </c>
       <c r="D115" t="n">
-        <v>0.02140475950392629</v>
+        <v>0.02140475950392623</v>
       </c>
     </row>
     <row r="116">
@@ -2382,10 +2382,10 @@
         <v>0.2166784744129847</v>
       </c>
       <c r="C117" t="n">
-        <v>0.5250216184338782</v>
+        <v>0.5250216184338781</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.3083431440208935</v>
+        <v>-0.3083431440208934</v>
       </c>
     </row>
     <row r="118">
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6548157053065889</v>
+        <v>0.6548157053065888</v>
       </c>
       <c r="C119" t="n">
         <v>0.3615755636834756</v>
       </c>
       <c r="D119" t="n">
-        <v>0.2932401416231133</v>
+        <v>0.2932401416231132</v>
       </c>
     </row>
     <row r="120">
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5389596698894611</v>
+        <v>0.5389596698894612</v>
       </c>
       <c r="C120" t="n">
         <v>0.5530873873626122</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.01412771747315111</v>
+        <v>-0.014127717473151</v>
       </c>
     </row>
     <row r="121">
@@ -2446,10 +2446,10 @@
         <v>0.7331868387061853</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2775608295367391</v>
+        <v>0.2775608295367392</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4556260091694462</v>
+        <v>0.4556260091694461</v>
       </c>
     </row>
     <row r="122">
@@ -2478,10 +2478,10 @@
         <v>0.7286654103748402</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3728797892852013</v>
+        <v>0.3728797892852014</v>
       </c>
       <c r="D123" t="n">
-        <v>0.355785621089639</v>
+        <v>0.3557856210896388</v>
       </c>
     </row>
     <row r="124">
@@ -2510,7 +2510,7 @@
         <v>0.2810848197779969</v>
       </c>
       <c r="C125" t="n">
-        <v>0.5589770737654575</v>
+        <v>0.5589770737654576</v>
       </c>
       <c r="D125" t="n">
         <v>-0.2778922539874606</v>
@@ -2526,10 +2526,10 @@
         <v>0.2906595706694708</v>
       </c>
       <c r="C126" t="n">
-        <v>0.5549963791033009</v>
+        <v>0.554996379103301</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.2643368084338301</v>
+        <v>-0.2643368084338302</v>
       </c>
     </row>
     <row r="127">
@@ -2539,13 +2539,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3503657345749583</v>
+        <v>0.3503657345749582</v>
       </c>
       <c r="C127" t="n">
-        <v>0.54800361784109</v>
+        <v>0.5480036178410901</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.1976378832661317</v>
+        <v>-0.1976378832661319</v>
       </c>
     </row>
     <row r="128">
@@ -2571,13 +2571,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4436491130658278</v>
+        <v>0.4436491130658279</v>
       </c>
       <c r="C129" t="n">
-        <v>0.4408269853055762</v>
+        <v>0.4408269853055763</v>
       </c>
       <c r="D129" t="n">
-        <v>0.002822127760251592</v>
+        <v>0.002822127760251647</v>
       </c>
     </row>
     <row r="130">
@@ -2590,10 +2590,10 @@
         <v>0.3982480010860507</v>
       </c>
       <c r="C130" t="n">
-        <v>0.6174430969208626</v>
+        <v>0.6174430969208629</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.2191950958348119</v>
+        <v>-0.2191950958348121</v>
       </c>
     </row>
     <row r="131">
@@ -2606,10 +2606,10 @@
         <v>0.6401740998721446</v>
       </c>
       <c r="C131" t="n">
-        <v>0.4853575215344047</v>
+        <v>0.4853575215344045</v>
       </c>
       <c r="D131" t="n">
-        <v>0.1548165783377399</v>
+        <v>0.15481657833774</v>
       </c>
     </row>
     <row r="132">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.2495821454653234</v>
+        <v>0.2495821454653235</v>
       </c>
       <c r="C132" t="n">
         <v>0.5333703062025809</v>
@@ -2638,10 +2638,10 @@
         <v>0.3326224677185819</v>
       </c>
       <c r="C133" t="n">
-        <v>0.6215009457109943</v>
+        <v>0.6215009457109945</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.2888784779924125</v>
+        <v>-0.2888784779924126</v>
       </c>
     </row>
     <row r="134">
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.3872696343614584</v>
+        <v>0.3872696343614585</v>
       </c>
       <c r="C134" t="n">
-        <v>0.4871511640342594</v>
+        <v>0.4871511640342596</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.09988152967280095</v>
+        <v>-0.09988152967280106</v>
       </c>
     </row>
     <row r="135">
@@ -2670,10 +2670,10 @@
         <v>0.271510068886523</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6528514943455954</v>
+        <v>0.6528514943455955</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.3813414254590725</v>
+        <v>-0.3813414254590726</v>
       </c>
     </row>
     <row r="136">
@@ -2686,10 +2686,10 @@
         <v>0.2730153928487399</v>
       </c>
       <c r="C136" t="n">
-        <v>0.5101492053888721</v>
+        <v>0.5101492053888722</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.2371338125401322</v>
+        <v>-0.2371338125401323</v>
       </c>
     </row>
     <row r="137">
@@ -2718,10 +2718,10 @@
         <v>0.3263348973686405</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4071858757528258</v>
+        <v>0.4071858757528256</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.08085097838418531</v>
+        <v>-0.08085097838418515</v>
       </c>
     </row>
     <row r="139">
@@ -2750,10 +2750,10 @@
         <v>0.4394157850143331</v>
       </c>
       <c r="C140" t="n">
-        <v>0.4099397433899538</v>
+        <v>0.4099397433899537</v>
       </c>
       <c r="D140" t="n">
-        <v>0.02947604162437928</v>
+        <v>0.02947604162437939</v>
       </c>
     </row>
     <row r="141">
@@ -2782,10 +2782,10 @@
         <v>0.2585595247916838</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4555523471660753</v>
+        <v>0.4555523471660755</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.1969928223743915</v>
+        <v>-0.1969928223743916</v>
       </c>
     </row>
     <row r="143">
@@ -2814,10 +2814,10 @@
         <v>0.2422277310487854</v>
       </c>
       <c r="C144" t="n">
-        <v>0.584604466689278</v>
+        <v>0.5846044666892781</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.3423767356404926</v>
+        <v>-0.3423767356404927</v>
       </c>
     </row>
     <row r="145">
@@ -2830,10 +2830,10 @@
         <v>0.3662978983084585</v>
       </c>
       <c r="C145" t="n">
-        <v>0.6374878921492237</v>
+        <v>0.6374878921492236</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.2711899938407652</v>
+        <v>-0.2711899938407651</v>
       </c>
     </row>
     <row r="146">
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.2310769406718585</v>
+        <v>0.2310769406718586</v>
       </c>
       <c r="C148" t="n">
         <v>0.5595744453305711</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.3284975046587126</v>
+        <v>-0.3284975046587125</v>
       </c>
     </row>
     <row r="149">
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.3421190823220359</v>
+        <v>0.3421190823220358</v>
       </c>
       <c r="C149" t="n">
-        <v>0.628821421041535</v>
+        <v>0.6288214210415349</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.2867023387194992</v>
+        <v>-0.2867023387194991</v>
       </c>
     </row>
     <row r="150">
@@ -2939,13 +2939,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.2582271181809174</v>
+        <v>0.2582271181809173</v>
       </c>
       <c r="C152" t="n">
         <v>0.5220943449843706</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.2638672268034532</v>
+        <v>-0.2638672268034533</v>
       </c>
     </row>
     <row r="153">
@@ -2977,7 +2977,7 @@
         <v>0.4662867016839461</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.1579312260980439</v>
+        <v>-0.157931226098044</v>
       </c>
     </row>
     <row r="155">
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.294806250379223</v>
+        <v>0.2948062503792229</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6016135143476122</v>
+        <v>0.6016135143476121</v>
       </c>
       <c r="D157" t="n">
         <v>-0.3068072639683893</v>
@@ -3083,13 +3083,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.3636654911302217</v>
+        <v>0.3636654911302218</v>
       </c>
       <c r="C161" t="n">
-        <v>0.5402973718706744</v>
+        <v>0.5402973718706743</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.1766318807404527</v>
+        <v>-0.1766318807404525</v>
       </c>
     </row>
     <row r="162">
@@ -3134,10 +3134,10 @@
         <v>0.3713804674121479</v>
       </c>
       <c r="C164" t="n">
-        <v>0.5506948454931294</v>
+        <v>0.5506948454931295</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.1793143780809815</v>
+        <v>-0.1793143780809816</v>
       </c>
     </row>
     <row r="165">
@@ -3150,10 +3150,10 @@
         <v>0.3344791867191009</v>
       </c>
       <c r="C165" t="n">
-        <v>0.5097748932828547</v>
+        <v>0.5097748932828546</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.1752957065637538</v>
+        <v>-0.1752957065637537</v>
       </c>
     </row>
     <row r="166">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.4330893647781694</v>
+        <v>0.4330893647781693</v>
       </c>
       <c r="C166" t="n">
-        <v>0.5378819129334764</v>
+        <v>0.5378819129334763</v>
       </c>
       <c r="D166" t="n">
         <v>-0.104792548155307</v>
@@ -3217,7 +3217,7 @@
         <v>0.4582932284648314</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.2349801538193585</v>
+        <v>-0.2349801538193584</v>
       </c>
     </row>
     <row r="170">
@@ -3230,10 +3230,10 @@
         <v>0.5346006253522135</v>
       </c>
       <c r="C170" t="n">
-        <v>0.4724139616887739</v>
+        <v>0.472413961688774</v>
       </c>
       <c r="D170" t="n">
-        <v>0.06218666366343961</v>
+        <v>0.06218666366343956</v>
       </c>
     </row>
     <row r="171">
@@ -3246,10 +3246,10 @@
         <v>0.3756674868794331</v>
       </c>
       <c r="C171" t="n">
-        <v>0.4824760822203277</v>
+        <v>0.4824760822203278</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.1068085953408945</v>
+        <v>-0.1068085953408947</v>
       </c>
     </row>
     <row r="172">
@@ -3281,7 +3281,7 @@
         <v>0.4728745947498526</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.09975941444054642</v>
+        <v>-0.09975941444054637</v>
       </c>
     </row>
     <row r="174">
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.3927444127097621</v>
+        <v>0.3927444127097622</v>
       </c>
       <c r="C174" t="n">
         <v>0.5742597023225684</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.1815152896128063</v>
+        <v>-0.1815152896128062</v>
       </c>
     </row>
     <row r="175">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.3461594704891462</v>
+        <v>0.3461594704891463</v>
       </c>
       <c r="C175" t="n">
-        <v>0.3706125273858959</v>
+        <v>0.3706125273858958</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.02445305689674965</v>
+        <v>-0.02445305689674954</v>
       </c>
     </row>
     <row r="176">
@@ -3329,7 +3329,7 @@
         <v>0.5553011761039152</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.3470531270011511</v>
+        <v>-0.347053127001151</v>
       </c>
     </row>
     <row r="177">
@@ -3342,10 +3342,10 @@
         <v>0.3020002453217534</v>
       </c>
       <c r="C177" t="n">
-        <v>0.5702981052168412</v>
+        <v>0.5702981052168414</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.2682978598950878</v>
+        <v>-0.268297859895088</v>
       </c>
     </row>
     <row r="178">
@@ -3361,7 +3361,7 @@
         <v>0.3129134620966978</v>
       </c>
       <c r="D178" t="n">
-        <v>0.3823541415943032</v>
+        <v>0.3823541415943033</v>
       </c>
     </row>
     <row r="179">
@@ -3390,10 +3390,10 @@
         <v>0.279848171152519</v>
       </c>
       <c r="C180" t="n">
-        <v>0.6474102185677139</v>
+        <v>0.6474102185677137</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.3675620474151949</v>
+        <v>-0.3675620474151948</v>
       </c>
     </row>
     <row r="181">
@@ -3422,10 +3422,10 @@
         <v>0.4112568200102232</v>
       </c>
       <c r="C182" t="n">
-        <v>0.4634854721068729</v>
+        <v>0.463485472106873</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.05222865209664967</v>
+        <v>-0.05222865209664979</v>
       </c>
     </row>
     <row r="183">
@@ -3454,10 +3454,10 @@
         <v>0.6989592159132626</v>
       </c>
       <c r="C184" t="n">
-        <v>0.3856728603861678</v>
+        <v>0.3856728603861679</v>
       </c>
       <c r="D184" t="n">
-        <v>0.3132863555270948</v>
+        <v>0.3132863555270947</v>
       </c>
     </row>
     <row r="185">
@@ -3470,10 +3470,10 @@
         <v>0.5613354582911551</v>
       </c>
       <c r="C185" t="n">
-        <v>0.3907337128399748</v>
+        <v>0.3907337128399747</v>
       </c>
       <c r="D185" t="n">
-        <v>0.1706017454511803</v>
+        <v>0.1706017454511804</v>
       </c>
     </row>
     <row r="186">
@@ -3489,7 +3489,7 @@
         <v>0.4359135659874048</v>
       </c>
       <c r="D186" t="n">
-        <v>0.2552595216051201</v>
+        <v>0.25525952160512</v>
       </c>
     </row>
     <row r="187">
@@ -3502,10 +3502,10 @@
         <v>0.5690547997288365</v>
       </c>
       <c r="C187" t="n">
-        <v>0.495627423479911</v>
+        <v>0.4956274234799108</v>
       </c>
       <c r="D187" t="n">
-        <v>0.07342737624892559</v>
+        <v>0.0734273762489257</v>
       </c>
     </row>
     <row r="188">
@@ -3537,7 +3537,7 @@
         <v>0.4789040752657616</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.2363177466716779</v>
+        <v>-0.2363177466716778</v>
       </c>
     </row>
     <row r="190">
@@ -3550,10 +3550,10 @@
         <v>0.2676401400516573</v>
       </c>
       <c r="C190" t="n">
-        <v>0.4497982534138791</v>
+        <v>0.4497982534138792</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.1821581133622219</v>
+        <v>-0.182158113362222</v>
       </c>
     </row>
     <row r="191">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2457170183017886</v>
+        <v>0.2457170183017885</v>
       </c>
       <c r="C193" t="n">
-        <v>0.5387749146721178</v>
+        <v>0.5387749146721177</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2930578963703292</v>
+        <v>-0.2930578963703291</v>
       </c>
     </row>
     <row r="194">
@@ -3630,10 +3630,10 @@
         <v>0.6307558398144983</v>
       </c>
       <c r="C195" t="n">
-        <v>0.3688662468259861</v>
+        <v>0.3688662468259862</v>
       </c>
       <c r="D195" t="n">
-        <v>0.2618895929885123</v>
+        <v>0.2618895929885122</v>
       </c>
     </row>
     <row r="196">
@@ -3643,13 +3643,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.68827680674888</v>
+        <v>0.6882768067488799</v>
       </c>
       <c r="C196" t="n">
         <v>0.3320931380188042</v>
       </c>
       <c r="D196" t="n">
-        <v>0.3561836687300758</v>
+        <v>0.3561836687300757</v>
       </c>
     </row>
     <row r="197">
@@ -3662,10 +3662,10 @@
         <v>0.2392847430385587</v>
       </c>
       <c r="C197" t="n">
-        <v>0.617110035536733</v>
+        <v>0.6171100355367328</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.3778252924981743</v>
+        <v>-0.3778252924981741</v>
       </c>
     </row>
     <row r="198">
@@ -3694,10 +3694,10 @@
         <v>0.4725839845054432</v>
       </c>
       <c r="C199" t="n">
-        <v>0.4719938154473259</v>
+        <v>0.4719938154473258</v>
       </c>
       <c r="D199" t="n">
-        <v>0.000590169058117318</v>
+        <v>0.0005901690581173735</v>
       </c>
     </row>
     <row r="200">
@@ -3710,10 +3710,10 @@
         <v>0.3353199157175727</v>
       </c>
       <c r="C200" t="n">
-        <v>0.3679258831473995</v>
+        <v>0.3679258831473996</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.03260596742982685</v>
+        <v>-0.03260596742982691</v>
       </c>
     </row>
     <row r="201">
@@ -3739,13 +3739,13 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.7203790352045447</v>
+        <v>0.7203790352045446</v>
       </c>
       <c r="C202" t="n">
         <v>0.3054356229011785</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4149434123033662</v>
+        <v>0.4149434123033661</v>
       </c>
     </row>
     <row r="203">
@@ -3758,10 +3758,10 @@
         <v>0.2845583924702809</v>
       </c>
       <c r="C203" t="n">
-        <v>0.4889509177521718</v>
+        <v>0.4889509177521717</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.2043925252818909</v>
+        <v>-0.2043925252818908</v>
       </c>
     </row>
     <row r="204">
@@ -3790,10 +3790,10 @@
         <v>0.5800641590592914</v>
       </c>
       <c r="C205" t="n">
-        <v>0.351754072362933</v>
+        <v>0.3517540723629329</v>
       </c>
       <c r="D205" t="n">
-        <v>0.2283100866963584</v>
+        <v>0.2283100866963585</v>
       </c>
     </row>
     <row r="206">
@@ -3822,10 +3822,10 @@
         <v>0.3527840308633973</v>
       </c>
       <c r="C207" t="n">
-        <v>0.5392355477331964</v>
+        <v>0.5392355477331963</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.1864515168697991</v>
+        <v>-0.186451516869799</v>
       </c>
     </row>
   </sheetData>
